--- a/assets/templates.xlsx
+++ b/assets/templates.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude\Claude Code\Auftragsdoku FlexPos NFK + BBA\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E985367-DA94-43E0-8602-F49577340957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9AA12BD-B44E-44AE-A1ED-90ACD41252EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NFK Vollverkabelung 3x43HE" sheetId="1" r:id="rId1"/>
-    <sheet name="NFK Vollverkabelung 2x47HE" sheetId="3" r:id="rId2"/>
+    <sheet name="Vollverkabelung 2x47HE" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -5257,7 +5257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="332" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
         <v>347</v>
       </c>
@@ -5271,7 +5271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333" s="2"/>
       <c r="B333" s="2"/>
       <c r="C333" s="5" t="s">
@@ -5281,7 +5281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="334" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" s="2"/>
       <c r="B334" s="2"/>
       <c r="C334" s="5" t="s">
@@ -5291,7 +5291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="335" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335" s="2"/>
       <c r="B335" s="2"/>
       <c r="C335" s="5" t="s">
@@ -5301,7 +5301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="336" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" s="2"/>
       <c r="B336" s="2"/>
       <c r="C336" s="5" t="s">
@@ -5311,7 +5311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="337" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A337" s="2"/>
       <c r="B337" s="2"/>
       <c r="C337" s="5" t="s">
@@ -5321,7 +5321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="338" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338" s="2"/>
       <c r="B338" s="2"/>
       <c r="C338" s="5" t="s">
@@ -5331,7 +5331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="339" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339" s="2"/>
       <c r="B339" s="2"/>
       <c r="C339" s="5" t="s">
@@ -5341,7 +5341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="340" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A340" s="2"/>
       <c r="B340" s="2"/>
       <c r="C340" s="5" t="s">
@@ -5351,7 +5351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="341" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A341" s="2"/>
       <c r="B341" s="2"/>
       <c r="C341" s="5" t="s">
@@ -5361,7 +5361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="342" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A342" s="2"/>
       <c r="B342" s="2"/>
       <c r="C342" s="5" t="s">
@@ -5371,7 +5371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="343" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343" s="2"/>
       <c r="B343" s="2"/>
       <c r="C343" s="5" t="s">
@@ -5381,7 +5381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="344" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344" s="2"/>
       <c r="B344" s="2" t="s">
         <v>365</v>
@@ -5393,7 +5393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="345" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A345" s="2"/>
       <c r="B345" s="2"/>
       <c r="C345" s="5" t="s">
@@ -5403,7 +5403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="346" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346" s="2"/>
       <c r="B346" s="2"/>
       <c r="C346" s="5" t="s">
@@ -5413,7 +5413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="347" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347" s="2"/>
       <c r="B347" s="2"/>
       <c r="C347" s="5" t="s">
@@ -5423,7 +5423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="348" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A348" s="2"/>
       <c r="B348" s="2"/>
       <c r="C348" s="5" t="s">
@@ -5433,7 +5433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="349" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A349" s="2"/>
       <c r="B349" s="2"/>
       <c r="C349" s="5" t="s">
@@ -5443,7 +5443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="350" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" s="2"/>
       <c r="B350" s="2"/>
       <c r="C350" s="5" t="s">
@@ -5453,7 +5453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="351" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" s="2"/>
       <c r="B351" s="2"/>
       <c r="C351" s="5" t="s">
@@ -5463,7 +5463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="352" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352" s="2"/>
       <c r="B352" s="2"/>
       <c r="C352" s="5" t="s">
@@ -5473,7 +5473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="353" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A353" s="2"/>
       <c r="B353" s="2"/>
       <c r="C353" s="5" t="s">
@@ -5483,7 +5483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="354" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A354" s="2"/>
       <c r="B354" s="2"/>
       <c r="C354" s="5" t="s">
@@ -5493,7 +5493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="355" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A355" s="2"/>
       <c r="B355" s="2"/>
       <c r="C355" s="5" t="s">
@@ -5503,7 +5503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="356" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
         <v>378</v>
       </c>
@@ -5517,7 +5517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="357" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A357" s="2"/>
       <c r="B357" s="2"/>
       <c r="C357" s="5" t="s">
@@ -5527,7 +5527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="358" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A358" s="2"/>
       <c r="B358" s="2"/>
       <c r="C358" s="5" t="s">
@@ -5537,7 +5537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="359" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A359" s="2"/>
       <c r="B359" s="2"/>
       <c r="C359" s="5" t="s">
@@ -5547,7 +5547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="360" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A360" s="2"/>
       <c r="B360" s="2"/>
       <c r="C360" s="5" t="s">
@@ -5557,7 +5557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="361" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A361" s="2"/>
       <c r="B361" s="2"/>
       <c r="C361" s="5" t="s">
@@ -5567,7 +5567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="362" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A362" s="2"/>
       <c r="B362" s="2"/>
       <c r="C362" s="5" t="s">
@@ -5577,7 +5577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="363" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A363" s="2"/>
       <c r="B363" s="2"/>
       <c r="C363" s="5" t="s">
@@ -5587,7 +5587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="364" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A364" s="2"/>
       <c r="B364" s="2" t="s">
         <v>387</v>
@@ -5599,7 +5599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="365" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A365" s="2"/>
       <c r="B365" s="2"/>
       <c r="C365" s="5" t="s">
@@ -5609,7 +5609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="366" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A366" s="2"/>
       <c r="B366" s="2"/>
       <c r="C366" s="5" t="s">
@@ -5619,7 +5619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="367" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A367" s="2"/>
       <c r="B367" s="2"/>
       <c r="C367" s="5" t="s">
@@ -5629,7 +5629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="368" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A368" s="2"/>
       <c r="B368" s="2"/>
       <c r="C368" s="5" t="s">
@@ -5639,7 +5639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="369" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A369" s="2"/>
       <c r="B369" s="2"/>
       <c r="C369" s="5" t="s">
@@ -5649,7 +5649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="370" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A370" s="2"/>
       <c r="B370" s="2"/>
       <c r="C370" s="5" t="s">
@@ -5659,7 +5659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="371" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A371" s="2"/>
       <c r="B371" s="2"/>
       <c r="C371" s="5" t="s">
@@ -5669,7 +5669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="372" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
         <v>450</v>
       </c>
@@ -5681,7 +5681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="373" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A373" s="2"/>
       <c r="B373" s="2"/>
       <c r="C373" s="5" t="s">
@@ -5691,7 +5691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="374" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A374" s="2"/>
       <c r="B374" s="2"/>
       <c r="C374" s="5" t="s">
@@ -5701,7 +5701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="375" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
         <v>392</v>
       </c>
@@ -5713,7 +5713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="376" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A376" s="2"/>
       <c r="B376" s="2"/>
       <c r="C376" s="5" t="s">
@@ -5723,7 +5723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="377" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A377" s="2"/>
       <c r="B377" s="2"/>
       <c r="C377" s="5" t="s">
@@ -5733,7 +5733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="378" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A378" s="2"/>
       <c r="B378" s="2"/>
       <c r="C378" s="5" t="s">
@@ -5743,7 +5743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="379" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A379" s="2"/>
       <c r="B379" s="2"/>
       <c r="C379" s="5" t="s">
@@ -5753,7 +5753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="380" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A380" s="2"/>
       <c r="B380" s="2"/>
       <c r="C380" s="5" t="s">
@@ -5763,7 +5763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="381" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
         <v>129</v>
       </c>
@@ -5775,7 +5775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="382" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A382" s="2"/>
       <c r="B382" s="2"/>
       <c r="C382" s="5" t="s">
@@ -5785,7 +5785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="383" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A383" s="2"/>
       <c r="B383" s="2"/>
       <c r="C383" s="5" t="s">
@@ -5795,7 +5795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="384" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A384" s="2"/>
       <c r="B384" s="2"/>
       <c r="C384" s="5" t="s">
@@ -5805,244 +5805,234 @@
         <v>1</v>
       </c>
     </row>
-    <row r="385" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A385" s="2"/>
       <c r="B385" s="2"/>
       <c r="C385" s="7"/>
       <c r="D385" s="3"/>
     </row>
-    <row r="386" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A386" s="2"/>
       <c r="B386" s="2"/>
       <c r="C386" s="7"/>
       <c r="D386" s="3"/>
     </row>
-    <row r="387" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A387" s="2"/>
       <c r="B387" s="2"/>
       <c r="C387" s="7"/>
       <c r="D387" s="3"/>
     </row>
-    <row r="388" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A388" s="2"/>
       <c r="B388" s="2"/>
       <c r="C388" s="7"/>
       <c r="D388" s="3"/>
     </row>
-    <row r="389" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A389" s="2"/>
       <c r="B389" s="2"/>
       <c r="C389" s="7"/>
       <c r="D389" s="3"/>
     </row>
-    <row r="390" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A390" s="2"/>
       <c r="B390" s="2"/>
       <c r="C390" s="7"/>
       <c r="D390" s="3"/>
     </row>
-    <row r="391" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A391" s="2"/>
       <c r="B391" s="2"/>
       <c r="C391" s="7"/>
       <c r="D391" s="3"/>
     </row>
-    <row r="392" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A392" s="2"/>
       <c r="B392" s="2"/>
       <c r="C392" s="7"/>
       <c r="D392" s="3"/>
     </row>
-    <row r="393" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A393" s="2"/>
       <c r="B393" s="2"/>
       <c r="C393" s="7"/>
       <c r="D393" s="3"/>
     </row>
-    <row r="394" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A394" s="2"/>
       <c r="B394" s="2"/>
       <c r="C394" s="7"/>
       <c r="D394" s="3"/>
     </row>
-    <row r="395" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A395" s="2"/>
       <c r="B395" s="2"/>
       <c r="C395" s="7"/>
       <c r="D395" s="3"/>
     </row>
-    <row r="396" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A396" s="2"/>
       <c r="B396" s="2"/>
       <c r="C396" s="7"/>
       <c r="D396" s="3"/>
     </row>
-    <row r="397" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A397" s="2"/>
       <c r="B397" s="2"/>
       <c r="C397" s="7"/>
       <c r="D397" s="3"/>
     </row>
-    <row r="398" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A398" s="2"/>
       <c r="B398" s="2"/>
       <c r="C398" s="7"/>
       <c r="D398" s="3"/>
     </row>
-    <row r="399" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A399" s="2"/>
       <c r="B399" s="2"/>
       <c r="C399" s="7"/>
       <c r="D399" s="3"/>
     </row>
-    <row r="400" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A400" s="2"/>
       <c r="B400" s="2"/>
       <c r="C400" s="7"/>
       <c r="D400" s="3"/>
     </row>
-    <row r="401" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A401" s="2"/>
       <c r="B401" s="2"/>
       <c r="C401" s="7"/>
       <c r="D401" s="3"/>
     </row>
-    <row r="402" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A402" s="2"/>
       <c r="B402" s="2"/>
       <c r="C402" s="7"/>
       <c r="D402" s="3"/>
     </row>
-    <row r="403" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A403" s="2"/>
       <c r="B403" s="2"/>
       <c r="C403" s="7"/>
       <c r="D403" s="3"/>
     </row>
-    <row r="404" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A404" s="2"/>
       <c r="B404" s="2"/>
       <c r="C404" s="7"/>
       <c r="D404" s="3"/>
     </row>
-    <row r="405" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A405" s="2"/>
       <c r="B405" s="2"/>
       <c r="C405" s="7"/>
       <c r="D405" s="3"/>
     </row>
-    <row r="406" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A406" s="2"/>
       <c r="B406" s="2"/>
       <c r="C406" s="7"/>
       <c r="D406" s="3"/>
     </row>
-    <row r="407" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A407" s="2"/>
       <c r="B407" s="2"/>
       <c r="C407" s="7"/>
       <c r="D407" s="3"/>
     </row>
-    <row r="408" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A408" s="2"/>
       <c r="B408" s="5"/>
       <c r="C408" s="7"/>
       <c r="D408" s="3"/>
     </row>
-    <row r="409" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A409" s="2"/>
       <c r="B409" s="2"/>
       <c r="C409" s="7"/>
       <c r="D409" s="3"/>
     </row>
-    <row r="410" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A410" s="2"/>
       <c r="B410" s="2"/>
       <c r="C410" s="7"/>
       <c r="D410" s="3"/>
     </row>
-    <row r="411" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A411" s="2"/>
       <c r="B411" s="2"/>
       <c r="C411" s="5"/>
       <c r="D411" s="3"/>
     </row>
-    <row r="412" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A412" s="2"/>
       <c r="B412" s="2"/>
       <c r="C412" s="5"/>
       <c r="D412" s="3"/>
     </row>
-    <row r="413" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A413" s="2"/>
       <c r="B413" s="2"/>
       <c r="C413" s="5"/>
       <c r="D413" s="3"/>
     </row>
-    <row r="414" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A414" s="2"/>
       <c r="B414" s="2"/>
       <c r="C414" s="5"/>
       <c r="D414" s="3"/>
     </row>
-    <row r="415" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A415" s="2"/>
       <c r="B415" s="2"/>
       <c r="C415" s="2"/>
       <c r="D415" s="3"/>
     </row>
-    <row r="416" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A416" s="2"/>
       <c r="B416" s="2"/>
       <c r="C416" s="2"/>
       <c r="D416" s="3"/>
     </row>
-    <row r="417" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A417" s="2"/>
       <c r="B417" s="2"/>
       <c r="C417" s="2"/>
       <c r="D417" s="3"/>
     </row>
-    <row r="418" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A418" s="2"/>
       <c r="B418" s="2"/>
       <c r="C418" s="2"/>
       <c r="D418" s="3"/>
     </row>
-    <row r="419" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A419" s="2"/>
       <c r="B419" s="2"/>
       <c r="C419" s="2"/>
       <c r="D419" s="3"/>
     </row>
-    <row r="420" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A420" s="2"/>
       <c r="B420" s="2"/>
       <c r="C420" s="2"/>
       <c r="D420" s="3"/>
     </row>
-    <row r="421" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A421" s="2"/>
       <c r="B421" s="2"/>
       <c r="C421" s="2"/>
       <c r="D421" s="3"/>
     </row>
-    <row r="422" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A422" s="2"/>
       <c r="B422" s="2"/>
       <c r="C422" s="2"/>
       <c r="D422" s="3"/>
     </row>
-    <row r="423" spans="1:4" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="424" spans="1:4" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="425" spans="1:4" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="426" spans="1:4" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="427" spans="1:4" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="428" spans="1:4" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="429" spans="1:4" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="430" spans="1:4" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="431" spans="1:4" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="432" spans="1:4" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="433" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="434" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="435" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -9651,7 +9641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="344" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
         <v>347</v>
       </c>
@@ -9665,7 +9655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="345" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A345" s="2"/>
       <c r="B345" s="2"/>
       <c r="C345" s="5" t="s">
@@ -9675,7 +9665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="346" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346" s="2"/>
       <c r="B346" s="2"/>
       <c r="C346" s="5" t="s">
@@ -9685,7 +9675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="347" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347" s="2"/>
       <c r="B347" s="2"/>
       <c r="C347" s="5" t="s">
@@ -9695,7 +9685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="348" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A348" s="2"/>
       <c r="B348" s="2"/>
       <c r="C348" s="5" t="s">
@@ -9705,7 +9695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="349" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A349" s="2"/>
       <c r="B349" s="2"/>
       <c r="C349" s="5" t="s">
@@ -9715,7 +9705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="350" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" s="2"/>
       <c r="B350" s="2"/>
       <c r="C350" s="5" t="s">
@@ -9725,7 +9715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="351" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" s="2"/>
       <c r="B351" s="2"/>
       <c r="C351" s="5" t="s">
@@ -9735,7 +9725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="352" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352" s="2"/>
       <c r="B352" s="2"/>
       <c r="C352" s="5" t="s">
@@ -9745,7 +9735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="353" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A353" s="2"/>
       <c r="B353" s="2"/>
       <c r="C353" s="5" t="s">
@@ -9755,7 +9745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="354" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A354" s="2"/>
       <c r="B354" s="2"/>
       <c r="C354" s="5" t="s">
@@ -9765,7 +9755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="355" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A355" s="2"/>
       <c r="B355" s="2"/>
       <c r="C355" s="5" t="s">
@@ -9775,7 +9765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="356" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A356" s="2"/>
       <c r="B356" s="2" t="s">
         <v>365</v>
@@ -9787,7 +9777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="357" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A357" s="2"/>
       <c r="B357" s="2"/>
       <c r="C357" s="5" t="s">
@@ -9797,7 +9787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="358" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A358" s="2"/>
       <c r="B358" s="2"/>
       <c r="C358" s="5" t="s">
@@ -9807,7 +9797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="359" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A359" s="2"/>
       <c r="B359" s="2"/>
       <c r="C359" s="5" t="s">
@@ -9817,7 +9807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="360" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A360" s="2"/>
       <c r="B360" s="2"/>
       <c r="C360" s="5" t="s">
@@ -9827,7 +9817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="361" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A361" s="2"/>
       <c r="B361" s="2"/>
       <c r="C361" s="5" t="s">
@@ -9837,7 +9827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="362" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A362" s="2"/>
       <c r="B362" s="2"/>
       <c r="C362" s="5" t="s">
@@ -9847,7 +9837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="363" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A363" s="2"/>
       <c r="B363" s="2"/>
       <c r="C363" s="5" t="s">
@@ -9857,7 +9847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="364" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A364" s="2"/>
       <c r="B364" s="2"/>
       <c r="C364" s="5" t="s">
@@ -9867,7 +9857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="365" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A365" s="2"/>
       <c r="B365" s="2"/>
       <c r="C365" s="5" t="s">
@@ -9877,7 +9867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="366" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A366" s="2"/>
       <c r="B366" s="2"/>
       <c r="C366" s="5" t="s">
@@ -9887,7 +9877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="367" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A367" s="2"/>
       <c r="B367" s="2"/>
       <c r="C367" s="5" t="s">
@@ -9897,7 +9887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="368" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A368" s="2"/>
       <c r="B368" s="2"/>
       <c r="C368" s="5" t="s">
@@ -9907,7 +9897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="369" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A369" s="2"/>
       <c r="B369" s="2"/>
       <c r="C369" s="5" t="s">
@@ -9917,7 +9907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="370" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A370" s="2"/>
       <c r="B370" s="2"/>
       <c r="C370" s="5" t="s">
@@ -9927,7 +9917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="371" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A371" s="2"/>
       <c r="B371" s="2"/>
       <c r="C371" s="5" t="s">
@@ -9937,7 +9927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="372" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
         <v>450</v>
       </c>
@@ -9949,7 +9939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="373" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A373" s="2"/>
       <c r="B373" s="2"/>
       <c r="C373" s="5" t="s">
@@ -9959,7 +9949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="374" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A374" s="2"/>
       <c r="B374" s="2"/>
       <c r="C374" s="5" t="s">
@@ -9969,7 +9959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="375" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
         <v>392</v>
       </c>
@@ -9981,7 +9971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="376" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A376" s="2"/>
       <c r="B376" s="2"/>
       <c r="C376" s="5" t="s">
@@ -9991,7 +9981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="377" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A377" s="2"/>
       <c r="B377" s="2"/>
       <c r="C377" s="5" t="s">
@@ -10001,7 +9991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="378" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A378" s="2"/>
       <c r="B378" s="2"/>
       <c r="C378" s="5" t="s">
@@ -10011,7 +10001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="379" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A379" s="2"/>
       <c r="B379" s="2"/>
       <c r="C379" s="5" t="s">
@@ -10021,7 +10011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="380" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A380" s="2"/>
       <c r="B380" s="2"/>
       <c r="C380" s="5" t="s">
@@ -10031,7 +10021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="381" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
         <v>129</v>
       </c>
@@ -10043,7 +10033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="382" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A382" s="2"/>
       <c r="B382" s="2"/>
       <c r="C382" s="5" t="s">
@@ -10053,7 +10043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="383" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A383" s="2"/>
       <c r="B383" s="2"/>
       <c r="C383" s="5" t="s">
@@ -10063,7 +10053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="384" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A384" s="2"/>
       <c r="B384" s="2"/>
       <c r="C384" s="5" t="s">
@@ -10073,244 +10063,234 @@
         <v>1</v>
       </c>
     </row>
-    <row r="385" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A385" s="2"/>
       <c r="B385" s="2"/>
       <c r="C385" s="7"/>
       <c r="D385" s="3"/>
     </row>
-    <row r="386" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A386" s="2"/>
       <c r="B386" s="2"/>
       <c r="C386" s="7"/>
       <c r="D386" s="3"/>
     </row>
-    <row r="387" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A387" s="2"/>
       <c r="B387" s="2"/>
       <c r="C387" s="7"/>
       <c r="D387" s="3"/>
     </row>
-    <row r="388" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A388" s="2"/>
       <c r="B388" s="2"/>
       <c r="C388" s="7"/>
       <c r="D388" s="3"/>
     </row>
-    <row r="389" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A389" s="2"/>
       <c r="B389" s="2"/>
       <c r="C389" s="7"/>
       <c r="D389" s="3"/>
     </row>
-    <row r="390" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A390" s="2"/>
       <c r="B390" s="2"/>
       <c r="C390" s="7"/>
       <c r="D390" s="3"/>
     </row>
-    <row r="391" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A391" s="2"/>
       <c r="B391" s="2"/>
       <c r="C391" s="7"/>
       <c r="D391" s="3"/>
     </row>
-    <row r="392" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A392" s="2"/>
       <c r="B392" s="2"/>
       <c r="C392" s="7"/>
       <c r="D392" s="3"/>
     </row>
-    <row r="393" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A393" s="2"/>
       <c r="B393" s="2"/>
       <c r="C393" s="7"/>
       <c r="D393" s="3"/>
     </row>
-    <row r="394" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A394" s="2"/>
       <c r="B394" s="2"/>
       <c r="C394" s="7"/>
       <c r="D394" s="3"/>
     </row>
-    <row r="395" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A395" s="2"/>
       <c r="B395" s="2"/>
       <c r="C395" s="7"/>
       <c r="D395" s="3"/>
     </row>
-    <row r="396" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A396" s="2"/>
       <c r="B396" s="2"/>
       <c r="C396" s="7"/>
       <c r="D396" s="3"/>
     </row>
-    <row r="397" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A397" s="2"/>
       <c r="B397" s="2"/>
       <c r="C397" s="7"/>
       <c r="D397" s="3"/>
     </row>
-    <row r="398" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A398" s="2"/>
       <c r="B398" s="2"/>
       <c r="C398" s="7"/>
       <c r="D398" s="3"/>
     </row>
-    <row r="399" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A399" s="2"/>
       <c r="B399" s="2"/>
       <c r="C399" s="7"/>
       <c r="D399" s="3"/>
     </row>
-    <row r="400" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A400" s="2"/>
       <c r="B400" s="2"/>
       <c r="C400" s="7"/>
       <c r="D400" s="3"/>
     </row>
-    <row r="401" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A401" s="2"/>
       <c r="B401" s="2"/>
       <c r="C401" s="7"/>
       <c r="D401" s="3"/>
     </row>
-    <row r="402" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A402" s="2"/>
       <c r="B402" s="2"/>
       <c r="C402" s="7"/>
       <c r="D402" s="3"/>
     </row>
-    <row r="403" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A403" s="2"/>
       <c r="B403" s="2"/>
       <c r="C403" s="7"/>
       <c r="D403" s="3"/>
     </row>
-    <row r="404" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A404" s="2"/>
       <c r="B404" s="2"/>
       <c r="C404" s="7"/>
       <c r="D404" s="3"/>
     </row>
-    <row r="405" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A405" s="2"/>
       <c r="B405" s="2"/>
       <c r="C405" s="7"/>
       <c r="D405" s="3"/>
     </row>
-    <row r="406" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A406" s="2"/>
       <c r="B406" s="2"/>
       <c r="C406" s="7"/>
       <c r="D406" s="3"/>
     </row>
-    <row r="407" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A407" s="2"/>
       <c r="B407" s="2"/>
       <c r="C407" s="7"/>
       <c r="D407" s="3"/>
     </row>
-    <row r="408" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A408" s="2"/>
       <c r="B408" s="5"/>
       <c r="C408" s="7"/>
       <c r="D408" s="3"/>
     </row>
-    <row r="409" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A409" s="2"/>
       <c r="B409" s="2"/>
       <c r="C409" s="7"/>
       <c r="D409" s="3"/>
     </row>
-    <row r="410" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A410" s="2"/>
       <c r="B410" s="2"/>
       <c r="C410" s="7"/>
       <c r="D410" s="3"/>
     </row>
-    <row r="411" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A411" s="2"/>
       <c r="B411" s="2"/>
       <c r="C411" s="5"/>
       <c r="D411" s="3"/>
     </row>
-    <row r="412" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A412" s="2"/>
       <c r="B412" s="2"/>
       <c r="C412" s="5"/>
       <c r="D412" s="3"/>
     </row>
-    <row r="413" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A413" s="2"/>
       <c r="B413" s="2"/>
       <c r="C413" s="5"/>
       <c r="D413" s="3"/>
     </row>
-    <row r="414" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A414" s="2"/>
       <c r="B414" s="2"/>
       <c r="C414" s="5"/>
       <c r="D414" s="3"/>
     </row>
-    <row r="415" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A415" s="2"/>
       <c r="B415" s="2"/>
       <c r="C415" s="2"/>
       <c r="D415" s="3"/>
     </row>
-    <row r="416" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A416" s="2"/>
       <c r="B416" s="2"/>
       <c r="C416" s="2"/>
       <c r="D416" s="3"/>
     </row>
-    <row r="417" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A417" s="2"/>
       <c r="B417" s="2"/>
       <c r="C417" s="2"/>
       <c r="D417" s="3"/>
     </row>
-    <row r="418" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A418" s="2"/>
       <c r="B418" s="2"/>
       <c r="C418" s="2"/>
       <c r="D418" s="3"/>
     </row>
-    <row r="419" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A419" s="2"/>
       <c r="B419" s="2"/>
       <c r="C419" s="2"/>
       <c r="D419" s="3"/>
     </row>
-    <row r="420" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A420" s="2"/>
       <c r="B420" s="2"/>
       <c r="C420" s="2"/>
       <c r="D420" s="3"/>
     </row>
-    <row r="421" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A421" s="2"/>
       <c r="B421" s="2"/>
       <c r="C421" s="2"/>
       <c r="D421" s="3"/>
     </row>
-    <row r="422" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A422" s="2"/>
       <c r="B422" s="2"/>
       <c r="C422" s="2"/>
       <c r="D422" s="3"/>
     </row>
-    <row r="423" spans="1:4" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="424" spans="1:4" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="425" spans="1:4" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="426" spans="1:4" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="427" spans="1:4" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="428" spans="1:4" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="429" spans="1:4" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="430" spans="1:4" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="431" spans="1:4" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="432" spans="1:4" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="433" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="434" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="435" customFormat="1" x14ac:dyDescent="0.25"/>

--- a/assets/templates.xlsx
+++ b/assets/templates.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude\Claude Code\Auftragsdoku FlexPos NFK + BBA\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Michael\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9AA12BD-B44E-44AE-A1ED-90ACD41252EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C307878-9762-4243-91DC-446C06237DAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NFK Vollverkabelung 3x43HE" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="911" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="477">
   <si>
     <t>Oberordner</t>
   </si>
@@ -1292,36 +1292,6 @@
     <t>SN SMC</t>
   </si>
   <si>
-    <t>SN Vocovo Controller 2</t>
-  </si>
-  <si>
-    <t>LIN Vocovo Controller 2</t>
-  </si>
-  <si>
-    <t>SN Vocovo Controller 5</t>
-  </si>
-  <si>
-    <t>LIN Vocovo Controller 5</t>
-  </si>
-  <si>
-    <t>LIN Vocovo Controller 4</t>
-  </si>
-  <si>
-    <t>SN Vocovo Controller 4</t>
-  </si>
-  <si>
-    <t>LIN Vocovo Controller 3</t>
-  </si>
-  <si>
-    <t>SN Vocovo Controller 3</t>
-  </si>
-  <si>
-    <t>LIN Vocovo Controller 1</t>
-  </si>
-  <si>
-    <t>SN Vocovo Controller 1</t>
-  </si>
-  <si>
     <t>SN Kundenterminal</t>
   </si>
   <si>
@@ -1383,6 +1353,105 @@
   </si>
   <si>
     <t>Brandschott Außenbantenne</t>
+  </si>
+  <si>
+    <t>Switch 4 gepatcht</t>
+  </si>
+  <si>
+    <t>SCO 89 Module im Kassentisch</t>
+  </si>
+  <si>
+    <t>SCO 89 Kabelreserve</t>
+  </si>
+  <si>
+    <t>Reservekasse</t>
+  </si>
+  <si>
+    <t>Reservekasse Keystone-Module</t>
+  </si>
+  <si>
+    <t>Reservekasse Kabelreserve auf Trasse</t>
+  </si>
+  <si>
+    <t>SN Vocovo Repeater 1</t>
+  </si>
+  <si>
+    <t>LIN Vocovo Repeater 1</t>
+  </si>
+  <si>
+    <t>SN Vocovo Repeater 2</t>
+  </si>
+  <si>
+    <t>LIN Vocovo Repeater 2</t>
+  </si>
+  <si>
+    <t>SN Vocovo Repeater 3</t>
+  </si>
+  <si>
+    <t>LIN Vocovo Repeater 3</t>
+  </si>
+  <si>
+    <t>SN Vocovo Repeater 4</t>
+  </si>
+  <si>
+    <t>LIN Vocovo Repeater 4</t>
+  </si>
+  <si>
+    <t>SN Vocovo Repeater 5</t>
+  </si>
+  <si>
+    <t>LIN Vocovo Repeater 5</t>
+  </si>
+  <si>
+    <t>Vocovo Registrierungsmodul</t>
+  </si>
+  <si>
+    <t>SN Vocovo Registrierungsmodul</t>
+  </si>
+  <si>
+    <t>SN Lautsprecherleiste Lili</t>
+  </si>
+  <si>
+    <t>SN KVM Switch</t>
+  </si>
+  <si>
+    <t>SCO Kasse 10</t>
+  </si>
+  <si>
+    <t>SCO Kasse 11</t>
+  </si>
+  <si>
+    <t>SCO Kasse 12</t>
+  </si>
+  <si>
+    <t>SCO 10 Module im Kassentisch</t>
+  </si>
+  <si>
+    <t>SCO 11 Module im Kassentisch</t>
+  </si>
+  <si>
+    <t>SCO 12 Module im Kassentisch</t>
+  </si>
+  <si>
+    <t>SCO 12 Kabelreserve</t>
+  </si>
+  <si>
+    <t>SCO 11 Kabelreserve</t>
+  </si>
+  <si>
+    <t>SCO 10 Kabelreserve</t>
+  </si>
+  <si>
+    <t>CCTV 3 Modul im Kassentisch</t>
+  </si>
+  <si>
+    <t>CCTV 4 Modul im Kassentisch</t>
+  </si>
+  <si>
+    <t>SN Main Unit 3</t>
+  </si>
+  <si>
+    <t>SN Main Unit 4</t>
   </si>
 </sst>
 </file>
@@ -1812,7 +1881,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D464"/>
+  <dimension ref="A1:D437"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.7109375" customWidth="1"/>
@@ -1837,7 +1906,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>411</v>
@@ -1873,7 +1942,7 @@
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="5" t="s">
-        <v>73</v>
+        <v>473</v>
       </c>
       <c r="D5" s="6">
         <v>1</v>
@@ -1883,7 +1952,7 @@
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="5" t="s">
-        <v>74</v>
+        <v>474</v>
       </c>
       <c r="D6" s="6">
         <v>1</v>
@@ -1893,7 +1962,7 @@
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D7" s="6">
         <v>1</v>
@@ -1903,7 +1972,7 @@
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="5" t="s">
-        <v>419</v>
+        <v>74</v>
       </c>
       <c r="D8" s="6">
         <v>1</v>
@@ -1913,7 +1982,7 @@
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="5" t="s">
-        <v>420</v>
+        <v>75</v>
       </c>
       <c r="D9" s="6">
         <v>1</v>
@@ -1923,61 +1992,59 @@
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="D10" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="D11" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="D12" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="D13" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D14" s="6">
         <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="3">
-        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
+      <c r="B15" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="C15" s="5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D15" s="3">
         <v>1</v>
@@ -1987,7 +2054,7 @@
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D16" s="3">
         <v>1</v>
@@ -1995,11 +2062,9 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
-      <c r="B17" s="2" t="s">
-        <v>33</v>
-      </c>
+      <c r="B17" s="2"/>
       <c r="C17" s="5" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D17" s="3">
         <v>1</v>
@@ -2007,9 +2072,11 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
+      <c r="B18" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="C18" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D18" s="3">
         <v>1</v>
@@ -2019,7 +2086,7 @@
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="5" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D19" s="3">
         <v>1</v>
@@ -2027,11 +2094,9 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
-      <c r="B20" s="2" t="s">
-        <v>34</v>
-      </c>
+      <c r="B20" s="2"/>
       <c r="C20" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D20" s="3">
         <v>1</v>
@@ -2039,9 +2104,11 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
+      <c r="B21" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="C21" s="5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D21" s="3">
         <v>1</v>
@@ -2051,7 +2118,7 @@
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D22" s="3">
         <v>1</v>
@@ -2059,11 +2126,9 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
-      <c r="B23" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="B23" s="2"/>
       <c r="C23" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D23" s="3">
         <v>1</v>
@@ -2071,9 +2136,11 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
+      <c r="B24" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="C24" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D24" s="3">
         <v>1</v>
@@ -2083,7 +2150,7 @@
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D25" s="3">
         <v>1</v>
@@ -2091,11 +2158,9 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
-      <c r="B26" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="B26" s="2"/>
       <c r="C26" s="5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D26" s="3">
         <v>1</v>
@@ -2103,9 +2168,11 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
+      <c r="B27" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="C27" s="5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D27" s="3">
         <v>1</v>
@@ -2115,7 +2182,7 @@
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D28" s="3">
         <v>1</v>
@@ -2123,11 +2190,9 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
-      <c r="B29" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="B29" s="2"/>
       <c r="C29" s="5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D29" s="3">
         <v>1</v>
@@ -2135,9 +2200,11 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
+      <c r="B30" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="C30" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D30" s="3">
         <v>1</v>
@@ -2147,7 +2214,7 @@
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="5" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D31" s="3">
         <v>1</v>
@@ -2155,11 +2222,9 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
-      <c r="B32" s="2" t="s">
-        <v>38</v>
-      </c>
+      <c r="B32" s="2"/>
       <c r="C32" s="5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D32" s="3">
         <v>1</v>
@@ -2167,9 +2232,11 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
+      <c r="B33" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="C33" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D33" s="3">
         <v>1</v>
@@ -2179,7 +2246,7 @@
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D34" s="3">
         <v>1</v>
@@ -2187,11 +2254,9 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
-      <c r="B35" s="2" t="s">
-        <v>39</v>
-      </c>
+      <c r="B35" s="2"/>
       <c r="C35" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D35" s="3">
         <v>1</v>
@@ -2199,9 +2264,11 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
+      <c r="B36" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="C36" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D36" s="3">
         <v>1</v>
@@ -2211,7 +2278,7 @@
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="5" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D37" s="3">
         <v>1</v>
@@ -2219,11 +2286,9 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
-      <c r="B38" s="2" t="s">
-        <v>40</v>
-      </c>
+      <c r="B38" s="2"/>
       <c r="C38" s="5" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="D38" s="3">
         <v>1</v>
@@ -2231,9 +2296,11 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
+      <c r="B39" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="C39" s="5" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D39" s="3">
         <v>1</v>
@@ -2241,11 +2308,9 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
-      <c r="B40" s="2" t="s">
-        <v>57</v>
-      </c>
+      <c r="B40" s="2"/>
       <c r="C40" s="5" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D40" s="3">
         <v>1</v>
@@ -2255,7 +2320,7 @@
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="5" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D41" s="3">
         <v>1</v>
@@ -2264,10 +2329,10 @@
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2" t="s">
-        <v>58</v>
+        <v>447</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>45</v>
+        <v>448</v>
       </c>
       <c r="D42" s="3">
         <v>1</v>
@@ -2277,7 +2342,7 @@
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="5" t="s">
-        <v>46</v>
+        <v>449</v>
       </c>
       <c r="D43" s="3">
         <v>1</v>
@@ -2286,10 +2351,10 @@
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D44" s="3">
         <v>1</v>
@@ -2299,7 +2364,7 @@
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="5" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D45" s="3">
         <v>1</v>
@@ -2308,10 +2373,10 @@
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D46" s="3">
         <v>1</v>
@@ -2321,7 +2386,7 @@
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="5" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D47" s="3">
         <v>1</v>
@@ -2330,10 +2395,10 @@
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D48" s="3">
         <v>1</v>
@@ -2343,7 +2408,7 @@
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="5" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D49" s="3">
         <v>1</v>
@@ -2352,10 +2417,10 @@
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D50" s="3">
         <v>1</v>
@@ -2365,7 +2430,7 @@
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="5" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D51" s="3">
         <v>1</v>
@@ -2374,10 +2439,10 @@
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D52" s="3">
         <v>1</v>
@@ -2387,7 +2452,7 @@
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D53" s="3">
         <v>1</v>
@@ -2396,10 +2461,10 @@
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D54" s="3">
         <v>1</v>
@@ -2409,7 +2474,7 @@
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D55" s="3">
         <v>1</v>
@@ -2418,10 +2483,10 @@
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="D56" s="3">
         <v>1</v>
@@ -2431,7 +2496,7 @@
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="5" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="D57" s="3">
         <v>1</v>
@@ -2439,9 +2504,11 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
-      <c r="B58" s="2"/>
+      <c r="B58" s="2" t="s">
+        <v>63</v>
+      </c>
       <c r="C58" s="5" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="D58" s="3">
         <v>1</v>
@@ -2451,7 +2518,7 @@
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="5" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="D59" s="3">
         <v>1</v>
@@ -2460,10 +2527,10 @@
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="2" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>76</v>
+        <v>445</v>
       </c>
       <c r="D60" s="3">
         <v>1</v>
@@ -2473,7 +2540,7 @@
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="5" t="s">
-        <v>77</v>
+        <v>446</v>
       </c>
       <c r="D61" s="3">
         <v>1</v>
@@ -2481,9 +2548,11 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
-      <c r="B62" s="2"/>
+      <c r="B62" s="2" t="s">
+        <v>464</v>
+      </c>
       <c r="C62" s="5" t="s">
-        <v>78</v>
+        <v>467</v>
       </c>
       <c r="D62" s="3">
         <v>1</v>
@@ -2493,7 +2562,7 @@
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="5" t="s">
-        <v>79</v>
+        <v>472</v>
       </c>
       <c r="D63" s="3">
         <v>1</v>
@@ -2501,9 +2570,11 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
-      <c r="B64" s="2"/>
+      <c r="B64" s="2" t="s">
+        <v>465</v>
+      </c>
       <c r="C64" s="5" t="s">
-        <v>80</v>
+        <v>468</v>
       </c>
       <c r="D64" s="3">
         <v>1</v>
@@ -2513,7 +2584,7 @@
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="5" t="s">
-        <v>81</v>
+        <v>471</v>
       </c>
       <c r="D65" s="3">
         <v>1</v>
@@ -2521,9 +2592,11 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
-      <c r="B66" s="2"/>
+      <c r="B66" s="2" t="s">
+        <v>466</v>
+      </c>
       <c r="C66" s="5" t="s">
-        <v>82</v>
+        <v>469</v>
       </c>
       <c r="D66" s="3">
         <v>1</v>
@@ -2533,7 +2606,7 @@
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="5" t="s">
-        <v>83</v>
+        <v>470</v>
       </c>
       <c r="D67" s="3">
         <v>1</v>
@@ -2541,9 +2614,11 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
-      <c r="B68" s="2"/>
+      <c r="B68" s="2" t="s">
+        <v>65</v>
+      </c>
       <c r="C68" s="5" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="D68" s="3">
         <v>1</v>
@@ -2553,19 +2628,17 @@
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="5" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="D69" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="2" t="s">
-        <v>87</v>
-      </c>
+      <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="5" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="D70" s="3">
         <v>1</v>
@@ -2575,7 +2648,7 @@
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="5" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="D71" s="3">
         <v>1</v>
@@ -2583,9 +2656,11 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
-      <c r="B72" s="2"/>
+      <c r="B72" s="2" t="s">
+        <v>86</v>
+      </c>
       <c r="C72" s="5" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="D72" s="3">
         <v>1</v>
@@ -2595,7 +2670,7 @@
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="5" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="D73" s="3">
         <v>1</v>
@@ -2605,7 +2680,7 @@
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="5" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="D74" s="3">
         <v>1</v>
@@ -2615,7 +2690,7 @@
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="5" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="D75" s="3">
         <v>1</v>
@@ -2625,7 +2700,7 @@
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="5" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="D76" s="3">
         <v>1</v>
@@ -2635,7 +2710,7 @@
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="5" t="s">
-        <v>434</v>
+        <v>81</v>
       </c>
       <c r="D77" s="3">
         <v>1</v>
@@ -2645,7 +2720,7 @@
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="5" t="s">
-        <v>435</v>
+        <v>82</v>
       </c>
       <c r="D78" s="3">
         <v>1</v>
@@ -2655,19 +2730,17 @@
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="5" t="s">
-        <v>403</v>
+        <v>83</v>
       </c>
       <c r="D79" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="2" t="s">
-        <v>95</v>
-      </c>
+      <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="5" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="D80" s="3">
         <v>1</v>
@@ -2677,17 +2750,19 @@
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="5" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="D81" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="2"/>
+      <c r="A82" s="2" t="s">
+        <v>87</v>
+      </c>
       <c r="B82" s="2"/>
       <c r="C82" s="5" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D82" s="3">
         <v>1</v>
@@ -2697,7 +2772,7 @@
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="5" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="D83" s="3">
         <v>1</v>
@@ -2707,7 +2782,7 @@
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="5" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D84" s="3">
         <v>1</v>
@@ -2717,7 +2792,7 @@
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="5" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="D85" s="3">
         <v>1</v>
@@ -2727,7 +2802,7 @@
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="5" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D86" s="3">
         <v>1</v>
@@ -2737,7 +2812,7 @@
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="5" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D87" s="3">
         <v>1</v>
@@ -2747,7 +2822,7 @@
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="5" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D88" s="3">
         <v>1</v>
@@ -2757,17 +2832,17 @@
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="5" t="s">
-        <v>399</v>
+        <v>424</v>
       </c>
       <c r="D89" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="5" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="D90" s="3">
         <v>1</v>
@@ -2777,31 +2852,29 @@
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="5" t="s">
-        <v>433</v>
+        <v>403</v>
       </c>
       <c r="D91" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="2"/>
+      <c r="A92" s="2" t="s">
+        <v>95</v>
+      </c>
       <c r="B92" s="2"/>
       <c r="C92" s="5" t="s">
-        <v>404</v>
+        <v>96</v>
       </c>
       <c r="D92" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>412</v>
-      </c>
+      <c r="A93" s="2"/>
+      <c r="B93" s="2"/>
       <c r="C93" s="5" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D93" s="3">
         <v>1</v>
@@ -2811,7 +2884,7 @@
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="5" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D94" s="3">
         <v>1</v>
@@ -2821,7 +2894,7 @@
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="5" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D95" s="3">
         <v>1</v>
@@ -2831,7 +2904,7 @@
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="5" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="D96" s="3">
         <v>1</v>
@@ -2841,7 +2914,7 @@
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="5" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D97" s="3">
         <v>1</v>
@@ -2851,7 +2924,7 @@
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="5" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="D98" s="3">
         <v>1</v>
@@ -2861,7 +2934,7 @@
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="5" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="D99" s="3">
         <v>1</v>
@@ -2871,7 +2944,7 @@
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="5" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="D100" s="3">
         <v>1</v>
@@ -2881,17 +2954,17 @@
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="5" t="s">
-        <v>114</v>
+        <v>399</v>
       </c>
       <c r="D101" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="5" t="s">
-        <v>115</v>
+        <v>427</v>
       </c>
       <c r="D102" s="3">
         <v>1</v>
@@ -2901,7 +2974,7 @@
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="5" t="s">
-        <v>116</v>
+        <v>423</v>
       </c>
       <c r="D103" s="3">
         <v>1</v>
@@ -2911,29 +2984,31 @@
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="5" t="s">
-        <v>118</v>
+        <v>404</v>
       </c>
       <c r="D104" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="2"/>
-      <c r="B105" s="2"/>
+      <c r="A105" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>412</v>
+      </c>
       <c r="C105" s="5" t="s">
-        <v>406</v>
+        <v>106</v>
       </c>
       <c r="D105" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="2"/>
-      <c r="B106" s="2" t="s">
-        <v>117</v>
-      </c>
+      <c r="B106" s="2"/>
       <c r="C106" s="5" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="D106" s="3">
         <v>1</v>
@@ -2943,7 +3018,7 @@
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="5" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="D107" s="3">
         <v>1</v>
@@ -2953,7 +3028,7 @@
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="5" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="D108" s="3">
         <v>1</v>
@@ -2963,7 +3038,7 @@
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="5" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="D109" s="3">
         <v>1</v>
@@ -2973,7 +3048,7 @@
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="5" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="D110" s="3">
         <v>1</v>
@@ -2983,7 +3058,7 @@
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="5" t="s">
-        <v>400</v>
+        <v>112</v>
       </c>
       <c r="D111" s="3">
         <v>1</v>
@@ -2993,7 +3068,7 @@
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="5" t="s">
-        <v>401</v>
+        <v>113</v>
       </c>
       <c r="D112" s="3">
         <v>1</v>
@@ -3003,7 +3078,7 @@
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="5" t="s">
-        <v>417</v>
+        <v>114</v>
       </c>
       <c r="D113" s="3">
         <v>1</v>
@@ -3013,7 +3088,7 @@
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="5" t="s">
-        <v>418</v>
+        <v>115</v>
       </c>
       <c r="D114" s="3">
         <v>1</v>
@@ -3023,7 +3098,7 @@
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="5" t="s">
-        <v>438</v>
+        <v>116</v>
       </c>
       <c r="D115" s="3">
         <v>1</v>
@@ -3033,7 +3108,7 @@
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="5" t="s">
-        <v>439</v>
+        <v>118</v>
       </c>
       <c r="D116" s="3">
         <v>1</v>
@@ -3043,17 +3118,19 @@
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="5" t="s">
-        <v>440</v>
+        <v>406</v>
       </c>
       <c r="D117" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="2"/>
-      <c r="B118" s="2"/>
+      <c r="B118" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="C118" s="5" t="s">
-        <v>441</v>
+        <v>119</v>
       </c>
       <c r="D118" s="3">
         <v>1</v>
@@ -3063,7 +3140,7 @@
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="5" t="s">
-        <v>442</v>
+        <v>120</v>
       </c>
       <c r="D119" s="3">
         <v>1</v>
@@ -3073,7 +3150,7 @@
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="5" t="s">
-        <v>443</v>
+        <v>121</v>
       </c>
       <c r="D120" s="3">
         <v>1</v>
@@ -3083,7 +3160,7 @@
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="5" t="s">
-        <v>444</v>
+        <v>122</v>
       </c>
       <c r="D121" s="3">
         <v>1</v>
@@ -3093,7 +3170,7 @@
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="5" t="s">
-        <v>445</v>
+        <v>123</v>
       </c>
       <c r="D122" s="3">
         <v>1</v>
@@ -3101,11 +3178,9 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="2"/>
-      <c r="B123" s="2" t="s">
-        <v>124</v>
-      </c>
+      <c r="B123" s="2"/>
       <c r="C123" s="5" t="s">
-        <v>125</v>
+        <v>400</v>
       </c>
       <c r="D123" s="3">
         <v>1</v>
@@ -3115,7 +3190,7 @@
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="5" t="s">
-        <v>126</v>
+        <v>401</v>
       </c>
       <c r="D124" s="3">
         <v>1</v>
@@ -3125,7 +3200,7 @@
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="5" t="s">
-        <v>127</v>
+        <v>417</v>
       </c>
       <c r="D125" s="3">
         <v>1</v>
@@ -3135,19 +3210,17 @@
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="5" t="s">
-        <v>128</v>
+        <v>418</v>
       </c>
       <c r="D126" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A127" s="2" t="s">
-        <v>134</v>
-      </c>
+      <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="5" t="s">
-        <v>135</v>
+        <v>428</v>
       </c>
       <c r="D127" s="3">
         <v>1</v>
@@ -3157,7 +3230,7 @@
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="5" t="s">
-        <v>136</v>
+        <v>429</v>
       </c>
       <c r="D128" s="3">
         <v>1</v>
@@ -3167,7 +3240,7 @@
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="5" t="s">
-        <v>137</v>
+        <v>430</v>
       </c>
       <c r="D129" s="3">
         <v>1</v>
@@ -3177,7 +3250,7 @@
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="5" t="s">
-        <v>138</v>
+        <v>431</v>
       </c>
       <c r="D130" s="3">
         <v>1</v>
@@ -3187,7 +3260,7 @@
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="5" t="s">
-        <v>139</v>
+        <v>432</v>
       </c>
       <c r="D131" s="3">
         <v>1</v>
@@ -3197,7 +3270,7 @@
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="5" t="s">
-        <v>140</v>
+        <v>433</v>
       </c>
       <c r="D132" s="3">
         <v>1</v>
@@ -3207,19 +3280,17 @@
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="5" t="s">
-        <v>407</v>
+        <v>434</v>
       </c>
       <c r="D133" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A134" s="2" t="s">
-        <v>141</v>
-      </c>
+      <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="5" t="s">
-        <v>142</v>
+        <v>435</v>
       </c>
       <c r="D134" s="3">
         <v>1</v>
@@ -3227,9 +3298,11 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="2"/>
-      <c r="B135" s="2"/>
+      <c r="B135" s="2" t="s">
+        <v>124</v>
+      </c>
       <c r="C135" s="5" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="D135" s="3">
         <v>1</v>
@@ -3239,7 +3312,7 @@
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="5" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="D136" s="3">
         <v>1</v>
@@ -3249,7 +3322,7 @@
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="5" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="D137" s="3">
         <v>1</v>
@@ -3259,21 +3332,19 @@
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="5" t="s">
-        <v>408</v>
+        <v>128</v>
       </c>
       <c r="D138" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="B139" s="2" t="s">
-        <v>195</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="B139" s="2"/>
       <c r="C139" s="5" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="D139" s="3">
         <v>1</v>
@@ -3283,7 +3354,7 @@
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="5" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="D140" s="3">
         <v>1</v>
@@ -3293,7 +3364,7 @@
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="5" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="D141" s="3">
         <v>1</v>
@@ -3303,7 +3374,7 @@
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="5" t="s">
-        <v>211</v>
+        <v>138</v>
       </c>
       <c r="D142" s="3">
         <v>1</v>
@@ -3313,7 +3384,7 @@
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="5" t="s">
-        <v>213</v>
+        <v>139</v>
       </c>
       <c r="D143" s="3">
         <v>1</v>
@@ -3323,7 +3394,7 @@
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="5" t="s">
-        <v>212</v>
+        <v>140</v>
       </c>
       <c r="D144" s="3">
         <v>1</v>
@@ -3333,19 +3404,19 @@
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="5" t="s">
-        <v>214</v>
+        <v>407</v>
       </c>
       <c r="D145" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A146" s="2"/>
-      <c r="B146" s="2" t="s">
-        <v>196</v>
-      </c>
+      <c r="A146" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B146" s="2"/>
       <c r="C146" s="5" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="D146" s="3">
         <v>1</v>
@@ -3355,7 +3426,7 @@
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="5" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="D147" s="3">
         <v>1</v>
@@ -3365,7 +3436,7 @@
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="5" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="D148" s="3">
         <v>1</v>
@@ -3375,7 +3446,7 @@
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="5" t="s">
-        <v>215</v>
+        <v>145</v>
       </c>
       <c r="D149" s="3">
         <v>1</v>
@@ -3385,17 +3456,21 @@
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="5" t="s">
-        <v>216</v>
+        <v>408</v>
       </c>
       <c r="D150" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A151" s="2"/>
-      <c r="B151" s="2"/>
+      <c r="A151" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>195</v>
+      </c>
       <c r="C151" s="5" t="s">
-        <v>217</v>
+        <v>146</v>
       </c>
       <c r="D151" s="3">
         <v>1</v>
@@ -3405,7 +3480,7 @@
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="5" t="s">
-        <v>218</v>
+        <v>147</v>
       </c>
       <c r="D152" s="3">
         <v>1</v>
@@ -3413,11 +3488,9 @@
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" s="2"/>
-      <c r="B153" s="2" t="s">
-        <v>197</v>
-      </c>
+      <c r="B153" s="2"/>
       <c r="C153" s="5" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D153" s="3">
         <v>1</v>
@@ -3427,7 +3500,7 @@
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="5" t="s">
-        <v>153</v>
+        <v>211</v>
       </c>
       <c r="D154" s="3">
         <v>1</v>
@@ -3437,7 +3510,7 @@
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="5" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="D155" s="3">
         <v>1</v>
@@ -3447,7 +3520,7 @@
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="5" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="D156" s="3">
         <v>1</v>
@@ -3457,7 +3530,7 @@
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="5" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="D157" s="3">
         <v>1</v>
@@ -3465,9 +3538,11 @@
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" s="2"/>
-      <c r="B158" s="2"/>
+      <c r="B158" s="2" t="s">
+        <v>196</v>
+      </c>
       <c r="C158" s="5" t="s">
-        <v>221</v>
+        <v>149</v>
       </c>
       <c r="D158" s="3">
         <v>1</v>
@@ -3477,7 +3552,7 @@
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="5" t="s">
-        <v>222</v>
+        <v>150</v>
       </c>
       <c r="D159" s="3">
         <v>1</v>
@@ -3485,11 +3560,9 @@
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" s="2"/>
-      <c r="B160" s="2" t="s">
-        <v>198</v>
-      </c>
+      <c r="B160" s="2"/>
       <c r="C160" s="5" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D160" s="3">
         <v>1</v>
@@ -3499,7 +3572,7 @@
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="5" t="s">
-        <v>156</v>
+        <v>215</v>
       </c>
       <c r="D161" s="3">
         <v>1</v>
@@ -3509,7 +3582,7 @@
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="5" t="s">
-        <v>157</v>
+        <v>216</v>
       </c>
       <c r="D162" s="3">
         <v>1</v>
@@ -3519,7 +3592,7 @@
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="5" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D163" s="3">
         <v>1</v>
@@ -3529,7 +3602,7 @@
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D164" s="3">
         <v>1</v>
@@ -3537,9 +3610,11 @@
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" s="2"/>
-      <c r="B165" s="2"/>
+      <c r="B165" s="2" t="s">
+        <v>197</v>
+      </c>
       <c r="C165" s="5" t="s">
-        <v>225</v>
+        <v>152</v>
       </c>
       <c r="D165" s="3">
         <v>1</v>
@@ -3549,7 +3624,7 @@
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="5" t="s">
-        <v>226</v>
+        <v>153</v>
       </c>
       <c r="D166" s="3">
         <v>1</v>
@@ -3557,11 +3632,9 @@
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" s="2"/>
-      <c r="B167" s="2" t="s">
-        <v>199</v>
-      </c>
+      <c r="B167" s="2"/>
       <c r="C167" s="5" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D167" s="3">
         <v>1</v>
@@ -3571,7 +3644,7 @@
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="5" t="s">
-        <v>159</v>
+        <v>219</v>
       </c>
       <c r="D168" s="3">
         <v>1</v>
@@ -3581,7 +3654,7 @@
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="5" t="s">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="D169" s="3">
         <v>1</v>
@@ -3591,7 +3664,7 @@
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="5" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="D170" s="3">
         <v>1</v>
@@ -3601,7 +3674,7 @@
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="5" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="D171" s="3">
         <v>1</v>
@@ -3609,9 +3682,11 @@
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" s="2"/>
-      <c r="B172" s="2"/>
+      <c r="B172" s="2" t="s">
+        <v>198</v>
+      </c>
       <c r="C172" s="5" t="s">
-        <v>229</v>
+        <v>155</v>
       </c>
       <c r="D172" s="3">
         <v>1</v>
@@ -3621,7 +3696,7 @@
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="5" t="s">
-        <v>230</v>
+        <v>156</v>
       </c>
       <c r="D173" s="3">
         <v>1</v>
@@ -3629,11 +3704,9 @@
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" s="2"/>
-      <c r="B174" s="2" t="s">
-        <v>200</v>
-      </c>
+      <c r="B174" s="2"/>
       <c r="C174" s="5" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D174" s="3">
         <v>1</v>
@@ -3643,7 +3716,7 @@
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="5" t="s">
-        <v>162</v>
+        <v>223</v>
       </c>
       <c r="D175" s="3">
         <v>1</v>
@@ -3653,7 +3726,7 @@
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="5" t="s">
-        <v>163</v>
+        <v>224</v>
       </c>
       <c r="D176" s="3">
         <v>1</v>
@@ -3663,7 +3736,7 @@
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="5" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="D177" s="3">
         <v>1</v>
@@ -3673,7 +3746,7 @@
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="5" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="D178" s="3">
         <v>1</v>
@@ -3681,9 +3754,11 @@
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" s="2"/>
-      <c r="B179" s="2"/>
+      <c r="B179" s="2" t="s">
+        <v>199</v>
+      </c>
       <c r="C179" s="5" t="s">
-        <v>233</v>
+        <v>158</v>
       </c>
       <c r="D179" s="3">
         <v>1</v>
@@ -3693,7 +3768,7 @@
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="5" t="s">
-        <v>234</v>
+        <v>159</v>
       </c>
       <c r="D180" s="3">
         <v>1</v>
@@ -3701,11 +3776,9 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" s="2"/>
-      <c r="B181" s="2" t="s">
-        <v>201</v>
-      </c>
+      <c r="B181" s="2"/>
       <c r="C181" s="5" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D181" s="3">
         <v>1</v>
@@ -3715,7 +3788,7 @@
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="5" t="s">
-        <v>165</v>
+        <v>227</v>
       </c>
       <c r="D182" s="3">
         <v>1</v>
@@ -3725,7 +3798,7 @@
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="5" t="s">
-        <v>166</v>
+        <v>228</v>
       </c>
       <c r="D183" s="3">
         <v>1</v>
@@ -3735,7 +3808,7 @@
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="5" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="D184" s="3">
         <v>1</v>
@@ -3745,7 +3818,7 @@
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="5" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="D185" s="3">
         <v>1</v>
@@ -3753,9 +3826,11 @@
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" s="2"/>
-      <c r="B186" s="2"/>
+      <c r="B186" s="2" t="s">
+        <v>200</v>
+      </c>
       <c r="C186" s="5" t="s">
-        <v>237</v>
+        <v>161</v>
       </c>
       <c r="D186" s="3">
         <v>1</v>
@@ -3765,7 +3840,7 @@
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="5" t="s">
-        <v>238</v>
+        <v>162</v>
       </c>
       <c r="D187" s="3">
         <v>1</v>
@@ -3773,11 +3848,9 @@
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" s="2"/>
-      <c r="B188" s="2" t="s">
-        <v>202</v>
-      </c>
+      <c r="B188" s="2"/>
       <c r="C188" s="5" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D188" s="3">
         <v>1</v>
@@ -3787,7 +3860,7 @@
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="5" t="s">
-        <v>168</v>
+        <v>231</v>
       </c>
       <c r="D189" s="3">
         <v>1</v>
@@ -3797,7 +3870,7 @@
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="5" t="s">
-        <v>169</v>
+        <v>232</v>
       </c>
       <c r="D190" s="3">
         <v>1</v>
@@ -3807,7 +3880,7 @@
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="5" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="D191" s="3">
         <v>1</v>
@@ -3817,7 +3890,7 @@
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="5" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="D192" s="3">
         <v>1</v>
@@ -3825,9 +3898,11 @@
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" s="2"/>
-      <c r="B193" s="2"/>
+      <c r="B193" s="2" t="s">
+        <v>201</v>
+      </c>
       <c r="C193" s="5" t="s">
-        <v>241</v>
+        <v>164</v>
       </c>
       <c r="D193" s="3">
         <v>1</v>
@@ -3837,7 +3912,7 @@
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="5" t="s">
-        <v>242</v>
+        <v>165</v>
       </c>
       <c r="D194" s="3">
         <v>1</v>
@@ -3845,11 +3920,9 @@
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" s="2"/>
-      <c r="B195" s="2" t="s">
-        <v>203</v>
-      </c>
+      <c r="B195" s="2"/>
       <c r="C195" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D195" s="3">
         <v>1</v>
@@ -3859,7 +3932,7 @@
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="5" t="s">
-        <v>171</v>
+        <v>235</v>
       </c>
       <c r="D196" s="3">
         <v>1</v>
@@ -3869,7 +3942,7 @@
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="5" t="s">
-        <v>172</v>
+        <v>236</v>
       </c>
       <c r="D197" s="3">
         <v>1</v>
@@ -3879,7 +3952,7 @@
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="5" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D198" s="3">
         <v>1</v>
@@ -3889,7 +3962,7 @@
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="5" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="D199" s="3">
         <v>1</v>
@@ -3897,9 +3970,11 @@
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" s="2"/>
-      <c r="B200" s="2"/>
+      <c r="B200" s="2" t="s">
+        <v>202</v>
+      </c>
       <c r="C200" s="5" t="s">
-        <v>245</v>
+        <v>167</v>
       </c>
       <c r="D200" s="3">
         <v>1</v>
@@ -3909,7 +3984,7 @@
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="5" t="s">
-        <v>246</v>
+        <v>168</v>
       </c>
       <c r="D201" s="3">
         <v>1</v>
@@ -3917,11 +3992,9 @@
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" s="2"/>
-      <c r="B202" s="2" t="s">
-        <v>204</v>
-      </c>
+      <c r="B202" s="2"/>
       <c r="C202" s="5" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D202" s="3">
         <v>1</v>
@@ -3931,7 +4004,7 @@
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="5" t="s">
-        <v>174</v>
+        <v>239</v>
       </c>
       <c r="D203" s="3">
         <v>1</v>
@@ -3941,7 +4014,7 @@
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="5" t="s">
-        <v>175</v>
+        <v>240</v>
       </c>
       <c r="D204" s="3">
         <v>1</v>
@@ -3951,7 +4024,7 @@
       <c r="A205" s="2"/>
       <c r="B205" s="2"/>
       <c r="C205" s="5" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D205" s="3">
         <v>1</v>
@@ -3961,7 +4034,7 @@
       <c r="A206" s="2"/>
       <c r="B206" s="2"/>
       <c r="C206" s="5" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="D206" s="3">
         <v>1</v>
@@ -3969,9 +4042,11 @@
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" s="2"/>
-      <c r="B207" s="2"/>
+      <c r="B207" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C207" s="5" t="s">
-        <v>249</v>
+        <v>170</v>
       </c>
       <c r="D207" s="3">
         <v>1</v>
@@ -3981,7 +4056,7 @@
       <c r="A208" s="2"/>
       <c r="B208" s="2"/>
       <c r="C208" s="5" t="s">
-        <v>250</v>
+        <v>171</v>
       </c>
       <c r="D208" s="3">
         <v>1</v>
@@ -3989,11 +4064,9 @@
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" s="2"/>
-      <c r="B209" s="2" t="s">
-        <v>205</v>
-      </c>
+      <c r="B209" s="2"/>
       <c r="C209" s="5" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D209" s="3">
         <v>1</v>
@@ -4003,7 +4076,7 @@
       <c r="A210" s="2"/>
       <c r="B210" s="2"/>
       <c r="C210" s="5" t="s">
-        <v>177</v>
+        <v>243</v>
       </c>
       <c r="D210" s="3">
         <v>1</v>
@@ -4013,7 +4086,7 @@
       <c r="A211" s="2"/>
       <c r="B211" s="2"/>
       <c r="C211" s="5" t="s">
-        <v>178</v>
+        <v>244</v>
       </c>
       <c r="D211" s="3">
         <v>1</v>
@@ -4023,7 +4096,7 @@
       <c r="A212" s="2"/>
       <c r="B212" s="2"/>
       <c r="C212" s="5" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="D212" s="3">
         <v>1</v>
@@ -4033,7 +4106,7 @@
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="5" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="D213" s="3">
         <v>1</v>
@@ -4041,9 +4114,11 @@
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" s="2"/>
-      <c r="B214" s="2"/>
+      <c r="B214" s="2" t="s">
+        <v>204</v>
+      </c>
       <c r="C214" s="5" t="s">
-        <v>253</v>
+        <v>173</v>
       </c>
       <c r="D214" s="3">
         <v>1</v>
@@ -4053,7 +4128,7 @@
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="5" t="s">
-        <v>254</v>
+        <v>174</v>
       </c>
       <c r="D215" s="3">
         <v>1</v>
@@ -4061,11 +4136,9 @@
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" s="2"/>
-      <c r="B216" s="2" t="s">
-        <v>206</v>
-      </c>
+      <c r="B216" s="2"/>
       <c r="C216" s="5" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D216" s="3">
         <v>1</v>
@@ -4075,7 +4148,7 @@
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="5" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="D217" s="3">
         <v>1</v>
@@ -4085,7 +4158,7 @@
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="5" t="s">
-        <v>181</v>
+        <v>248</v>
       </c>
       <c r="D218" s="3">
         <v>1</v>
@@ -4095,7 +4168,7 @@
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="5" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="D219" s="3">
         <v>1</v>
@@ -4105,7 +4178,7 @@
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="5" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="D220" s="3">
         <v>1</v>
@@ -4113,9 +4186,11 @@
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" s="2"/>
-      <c r="B221" s="2"/>
+      <c r="B221" s="2" t="s">
+        <v>205</v>
+      </c>
       <c r="C221" s="5" t="s">
-        <v>257</v>
+        <v>176</v>
       </c>
       <c r="D221" s="3">
         <v>1</v>
@@ -4125,7 +4200,7 @@
       <c r="A222" s="2"/>
       <c r="B222" s="2"/>
       <c r="C222" s="5" t="s">
-        <v>258</v>
+        <v>177</v>
       </c>
       <c r="D222" s="3">
         <v>1</v>
@@ -4133,11 +4208,9 @@
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" s="2"/>
-      <c r="B223" s="2" t="s">
-        <v>207</v>
-      </c>
+      <c r="B223" s="2"/>
       <c r="C223" s="5" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D223" s="3">
         <v>1</v>
@@ -4147,7 +4220,7 @@
       <c r="A224" s="2"/>
       <c r="B224" s="2"/>
       <c r="C224" s="5" t="s">
-        <v>183</v>
+        <v>251</v>
       </c>
       <c r="D224" s="3">
         <v>1</v>
@@ -4157,7 +4230,7 @@
       <c r="A225" s="2"/>
       <c r="B225" s="2"/>
       <c r="C225" s="5" t="s">
-        <v>184</v>
+        <v>252</v>
       </c>
       <c r="D225" s="3">
         <v>1</v>
@@ -4167,7 +4240,7 @@
       <c r="A226" s="2"/>
       <c r="B226" s="2"/>
       <c r="C226" s="5" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="D226" s="3">
         <v>1</v>
@@ -4177,7 +4250,7 @@
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="5" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="D227" s="3">
         <v>1</v>
@@ -4185,9 +4258,11 @@
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" s="2"/>
-      <c r="B228" s="2"/>
+      <c r="B228" s="2" t="s">
+        <v>206</v>
+      </c>
       <c r="C228" s="5" t="s">
-        <v>261</v>
+        <v>179</v>
       </c>
       <c r="D228" s="3">
         <v>1</v>
@@ -4197,7 +4272,7 @@
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
       <c r="C229" s="5" t="s">
-        <v>262</v>
+        <v>180</v>
       </c>
       <c r="D229" s="3">
         <v>1</v>
@@ -4205,11 +4280,9 @@
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" s="2"/>
-      <c r="B230" s="2" t="s">
-        <v>208</v>
-      </c>
+      <c r="B230" s="2"/>
       <c r="C230" s="5" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D230" s="3">
         <v>1</v>
@@ -4219,7 +4292,7 @@
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
       <c r="C231" s="5" t="s">
-        <v>186</v>
+        <v>255</v>
       </c>
       <c r="D231" s="3">
         <v>1</v>
@@ -4229,7 +4302,7 @@
       <c r="A232" s="2"/>
       <c r="B232" s="2"/>
       <c r="C232" s="5" t="s">
-        <v>187</v>
+        <v>256</v>
       </c>
       <c r="D232" s="3">
         <v>1</v>
@@ -4239,7 +4312,7 @@
       <c r="A233" s="2"/>
       <c r="B233" s="2"/>
       <c r="C233" s="5" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="D233" s="3">
         <v>1</v>
@@ -4249,7 +4322,7 @@
       <c r="A234" s="2"/>
       <c r="B234" s="2"/>
       <c r="C234" s="5" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="D234" s="3">
         <v>1</v>
@@ -4257,9 +4330,11 @@
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" s="2"/>
-      <c r="B235" s="2"/>
+      <c r="B235" s="2" t="s">
+        <v>207</v>
+      </c>
       <c r="C235" s="5" t="s">
-        <v>265</v>
+        <v>182</v>
       </c>
       <c r="D235" s="3">
         <v>1</v>
@@ -4269,7 +4344,7 @@
       <c r="A236" s="2"/>
       <c r="B236" s="2"/>
       <c r="C236" s="5" t="s">
-        <v>266</v>
+        <v>183</v>
       </c>
       <c r="D236" s="3">
         <v>1</v>
@@ -4277,11 +4352,9 @@
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" s="2"/>
-      <c r="B237" s="2" t="s">
-        <v>209</v>
-      </c>
+      <c r="B237" s="2"/>
       <c r="C237" s="5" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D237" s="3">
         <v>1</v>
@@ -4291,7 +4364,7 @@
       <c r="A238" s="2"/>
       <c r="B238" s="2"/>
       <c r="C238" s="5" t="s">
-        <v>189</v>
+        <v>259</v>
       </c>
       <c r="D238" s="3">
         <v>1</v>
@@ -4301,7 +4374,7 @@
       <c r="A239" s="2"/>
       <c r="B239" s="2"/>
       <c r="C239" s="5" t="s">
-        <v>190</v>
+        <v>260</v>
       </c>
       <c r="D239" s="3">
         <v>1</v>
@@ -4311,7 +4384,7 @@
       <c r="A240" s="2"/>
       <c r="B240" s="2"/>
       <c r="C240" s="5" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D240" s="3">
         <v>1</v>
@@ -4321,7 +4394,7 @@
       <c r="A241" s="2"/>
       <c r="B241" s="2"/>
       <c r="C241" s="5" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="D241" s="3">
         <v>1</v>
@@ -4329,9 +4402,11 @@
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" s="2"/>
-      <c r="B242" s="2"/>
+      <c r="B242" s="2" t="s">
+        <v>208</v>
+      </c>
       <c r="C242" s="5" t="s">
-        <v>269</v>
+        <v>185</v>
       </c>
       <c r="D242" s="3">
         <v>1</v>
@@ -4341,7 +4416,7 @@
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="5" t="s">
-        <v>270</v>
+        <v>186</v>
       </c>
       <c r="D243" s="3">
         <v>1</v>
@@ -4349,11 +4424,9 @@
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" s="2"/>
-      <c r="B244" s="2" t="s">
-        <v>210</v>
-      </c>
+      <c r="B244" s="2"/>
       <c r="C244" s="5" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D244" s="3">
         <v>1</v>
@@ -4363,7 +4436,7 @@
       <c r="A245" s="2"/>
       <c r="B245" s="2"/>
       <c r="C245" s="5" t="s">
-        <v>192</v>
+        <v>263</v>
       </c>
       <c r="D245" s="3">
         <v>1</v>
@@ -4373,7 +4446,7 @@
       <c r="A246" s="2"/>
       <c r="B246" s="2"/>
       <c r="C246" s="5" t="s">
-        <v>193</v>
+        <v>264</v>
       </c>
       <c r="D246" s="3">
         <v>1</v>
@@ -4382,8 +4455,8 @@
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" s="2"/>
       <c r="B247" s="2"/>
-      <c r="C247" s="7" t="s">
-        <v>271</v>
+      <c r="C247" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="D247" s="3">
         <v>1</v>
@@ -4392,8 +4465,8 @@
     <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" s="2"/>
       <c r="B248" s="2"/>
-      <c r="C248" s="7" t="s">
-        <v>272</v>
+      <c r="C248" s="5" t="s">
+        <v>266</v>
       </c>
       <c r="D248" s="3">
         <v>1</v>
@@ -4401,9 +4474,11 @@
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" s="2"/>
-      <c r="B249" s="2"/>
-      <c r="C249" s="7" t="s">
-        <v>273</v>
+      <c r="B249" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C249" s="5" t="s">
+        <v>188</v>
       </c>
       <c r="D249" s="3">
         <v>1</v>
@@ -4412,22 +4487,18 @@
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" s="2"/>
       <c r="B250" s="2"/>
-      <c r="C250" s="7" t="s">
-        <v>274</v>
+      <c r="C250" s="5" t="s">
+        <v>189</v>
       </c>
       <c r="D250" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A251" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="B251" s="2" t="s">
-        <v>413</v>
-      </c>
+      <c r="A251" s="2"/>
+      <c r="B251" s="2"/>
       <c r="C251" s="5" t="s">
-        <v>276</v>
+        <v>190</v>
       </c>
       <c r="D251" s="3">
         <v>1</v>
@@ -4437,7 +4508,7 @@
       <c r="A252" s="2"/>
       <c r="B252" s="2"/>
       <c r="C252" s="5" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="D252" s="3">
         <v>1</v>
@@ -4447,7 +4518,7 @@
       <c r="A253" s="2"/>
       <c r="B253" s="2"/>
       <c r="C253" s="5" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="D253" s="3">
         <v>1</v>
@@ -4457,7 +4528,7 @@
       <c r="A254" s="2"/>
       <c r="B254" s="2"/>
       <c r="C254" s="5" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="D254" s="3">
         <v>1</v>
@@ -4467,7 +4538,7 @@
       <c r="A255" s="2"/>
       <c r="B255" s="2"/>
       <c r="C255" s="5" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="D255" s="3">
         <v>1</v>
@@ -4475,9 +4546,11 @@
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" s="2"/>
-      <c r="B256" s="2"/>
+      <c r="B256" s="2" t="s">
+        <v>210</v>
+      </c>
       <c r="C256" s="5" t="s">
-        <v>281</v>
+        <v>191</v>
       </c>
       <c r="D256" s="3">
         <v>1</v>
@@ -4487,7 +4560,7 @@
       <c r="A257" s="2"/>
       <c r="B257" s="2"/>
       <c r="C257" s="5" t="s">
-        <v>282</v>
+        <v>192</v>
       </c>
       <c r="D257" s="3">
         <v>1</v>
@@ -4497,7 +4570,7 @@
       <c r="A258" s="2"/>
       <c r="B258" s="2"/>
       <c r="C258" s="5" t="s">
-        <v>446</v>
+        <v>193</v>
       </c>
       <c r="D258" s="3">
         <v>1</v>
@@ -4506,8 +4579,8 @@
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" s="2"/>
       <c r="B259" s="2"/>
-      <c r="C259" s="5" t="s">
-        <v>447</v>
+      <c r="C259" s="7" t="s">
+        <v>271</v>
       </c>
       <c r="D259" s="3">
         <v>1</v>
@@ -4516,8 +4589,8 @@
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" s="2"/>
       <c r="B260" s="2"/>
-      <c r="C260" s="5" t="s">
-        <v>283</v>
+      <c r="C260" s="7" t="s">
+        <v>272</v>
       </c>
       <c r="D260" s="3">
         <v>1</v>
@@ -4526,8 +4599,8 @@
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" s="2"/>
       <c r="B261" s="2"/>
-      <c r="C261" s="5" t="s">
-        <v>284</v>
+      <c r="C261" s="7" t="s">
+        <v>273</v>
       </c>
       <c r="D261" s="3">
         <v>1</v>
@@ -4536,20 +4609,22 @@
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" s="2"/>
       <c r="B262" s="2"/>
-      <c r="C262" s="5" t="s">
-        <v>409</v>
+      <c r="C262" s="7" t="s">
+        <v>274</v>
       </c>
       <c r="D262" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A263" s="2"/>
+      <c r="A263" s="2" t="s">
+        <v>275</v>
+      </c>
       <c r="B263" s="2" t="s">
-        <v>117</v>
+        <v>413</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="D263" s="3">
         <v>1</v>
@@ -4559,7 +4634,7 @@
       <c r="A264" s="2"/>
       <c r="B264" s="2"/>
       <c r="C264" s="5" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="D264" s="3">
         <v>1</v>
@@ -4569,7 +4644,7 @@
       <c r="A265" s="2"/>
       <c r="B265" s="2"/>
       <c r="C265" s="5" t="s">
-        <v>346</v>
+        <v>278</v>
       </c>
       <c r="D265" s="3">
         <v>1</v>
@@ -4579,7 +4654,7 @@
       <c r="A266" s="2"/>
       <c r="B266" s="2"/>
       <c r="C266" s="5" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="D266" s="3">
         <v>1</v>
@@ -4589,21 +4664,17 @@
       <c r="A267" s="2"/>
       <c r="B267" s="2"/>
       <c r="C267" s="5" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="D267" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A268" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="B268" s="2" t="s">
-        <v>290</v>
-      </c>
+      <c r="A268" s="2"/>
+      <c r="B268" s="2"/>
       <c r="C268" s="5" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="D268" s="3">
         <v>1</v>
@@ -4613,7 +4684,7 @@
       <c r="A269" s="2"/>
       <c r="B269" s="2"/>
       <c r="C269" s="5" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="D269" s="3">
         <v>1</v>
@@ -4623,7 +4694,7 @@
       <c r="A270" s="2"/>
       <c r="B270" s="2"/>
       <c r="C270" s="5" t="s">
-        <v>293</v>
+        <v>436</v>
       </c>
       <c r="D270" s="3">
         <v>1</v>
@@ -4633,7 +4704,7 @@
       <c r="A271" s="2"/>
       <c r="B271" s="2"/>
       <c r="C271" s="5" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="D271" s="3">
         <v>1</v>
@@ -4643,7 +4714,7 @@
       <c r="A272" s="2"/>
       <c r="B272" s="2"/>
       <c r="C272" s="5" t="s">
-        <v>431</v>
+        <v>283</v>
       </c>
       <c r="D272" s="3">
         <v>1</v>
@@ -4651,11 +4722,9 @@
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" s="2"/>
-      <c r="B273" s="2" t="s">
-        <v>306</v>
-      </c>
+      <c r="B273" s="2"/>
       <c r="C273" s="5" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="D273" s="3">
         <v>1</v>
@@ -4665,17 +4734,19 @@
       <c r="A274" s="2"/>
       <c r="B274" s="2"/>
       <c r="C274" s="5" t="s">
-        <v>295</v>
+        <v>409</v>
       </c>
       <c r="D274" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" s="2"/>
-      <c r="B275" s="2"/>
+      <c r="B275" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="C275" s="5" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="D275" s="3">
         <v>1</v>
@@ -4685,7 +4756,7 @@
       <c r="A276" s="2"/>
       <c r="B276" s="2"/>
       <c r="C276" s="5" t="s">
-        <v>423</v>
+        <v>286</v>
       </c>
       <c r="D276" s="3">
         <v>1</v>
@@ -4695,7 +4766,7 @@
       <c r="A277" s="2"/>
       <c r="B277" s="2"/>
       <c r="C277" s="5" t="s">
-        <v>424</v>
+        <v>462</v>
       </c>
       <c r="D277" s="3">
         <v>1</v>
@@ -4703,11 +4774,9 @@
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" s="2"/>
-      <c r="B278" s="2" t="s">
-        <v>307</v>
-      </c>
+      <c r="B278" s="2"/>
       <c r="C278" s="5" t="s">
-        <v>297</v>
+        <v>463</v>
       </c>
       <c r="D278" s="3">
         <v>1</v>
@@ -4717,7 +4786,7 @@
       <c r="A279" s="2"/>
       <c r="B279" s="2"/>
       <c r="C279" s="5" t="s">
-        <v>298</v>
+        <v>346</v>
       </c>
       <c r="D279" s="3">
         <v>1</v>
@@ -4727,7 +4796,7 @@
       <c r="A280" s="2"/>
       <c r="B280" s="2"/>
       <c r="C280" s="5" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="D280" s="3">
         <v>1</v>
@@ -4737,17 +4806,21 @@
       <c r="A281" s="2"/>
       <c r="B281" s="2"/>
       <c r="C281" s="5" t="s">
-        <v>430</v>
+        <v>288</v>
       </c>
       <c r="D281" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A282" s="2"/>
-      <c r="B282" s="2"/>
+      <c r="A282" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="B282" s="2" t="s">
+        <v>290</v>
+      </c>
       <c r="C282" s="5" t="s">
-        <v>429</v>
+        <v>291</v>
       </c>
       <c r="D282" s="3">
         <v>1</v>
@@ -4755,11 +4828,9 @@
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" s="2"/>
-      <c r="B283" s="2" t="s">
-        <v>308</v>
-      </c>
+      <c r="B283" s="2"/>
       <c r="C283" s="5" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="D283" s="3">
         <v>1</v>
@@ -4769,7 +4840,7 @@
       <c r="A284" s="2"/>
       <c r="B284" s="2"/>
       <c r="C284" s="5" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="D284" s="3">
         <v>1</v>
@@ -4779,7 +4850,7 @@
       <c r="A285" s="2"/>
       <c r="B285" s="2"/>
       <c r="C285" s="5" t="s">
-        <v>302</v>
+        <v>450</v>
       </c>
       <c r="D285" s="3">
         <v>1</v>
@@ -4789,7 +4860,7 @@
       <c r="A286" s="2"/>
       <c r="B286" s="2"/>
       <c r="C286" s="5" t="s">
-        <v>428</v>
+        <v>451</v>
       </c>
       <c r="D286" s="3">
         <v>1</v>
@@ -4797,9 +4868,11 @@
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" s="2"/>
-      <c r="B287" s="2"/>
+      <c r="B287" s="2" t="s">
+        <v>306</v>
+      </c>
       <c r="C287" s="5" t="s">
-        <v>427</v>
+        <v>294</v>
       </c>
       <c r="D287" s="3">
         <v>1</v>
@@ -4807,11 +4880,9 @@
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" s="2"/>
-      <c r="B288" s="2" t="s">
-        <v>309</v>
-      </c>
+      <c r="B288" s="2"/>
       <c r="C288" s="5" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D288" s="3">
         <v>1</v>
@@ -4821,7 +4892,7 @@
       <c r="A289" s="2"/>
       <c r="B289" s="2"/>
       <c r="C289" s="5" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="D289" s="3">
         <v>1</v>
@@ -4831,7 +4902,7 @@
       <c r="A290" s="2"/>
       <c r="B290" s="2"/>
       <c r="C290" s="5" t="s">
-        <v>305</v>
+        <v>452</v>
       </c>
       <c r="D290" s="3">
         <v>1</v>
@@ -4841,7 +4912,7 @@
       <c r="A291" s="2"/>
       <c r="B291" s="2"/>
       <c r="C291" s="5" t="s">
-        <v>425</v>
+        <v>453</v>
       </c>
       <c r="D291" s="3">
         <v>1</v>
@@ -4849,9 +4920,11 @@
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" s="2"/>
-      <c r="B292" s="2"/>
+      <c r="B292" s="2" t="s">
+        <v>307</v>
+      </c>
       <c r="C292" s="5" t="s">
-        <v>426</v>
+        <v>297</v>
       </c>
       <c r="D292" s="3">
         <v>1</v>
@@ -4859,11 +4932,9 @@
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" s="2"/>
-      <c r="B293" s="2" t="s">
-        <v>312</v>
-      </c>
+      <c r="B293" s="2"/>
       <c r="C293" s="5" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="D293" s="3">
         <v>1</v>
@@ -4873,19 +4944,17 @@
       <c r="A294" s="2"/>
       <c r="B294" s="2"/>
       <c r="C294" s="5" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="D294" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A295" s="2" t="s">
-        <v>313</v>
-      </c>
+      <c r="A295" s="2"/>
       <c r="B295" s="2"/>
       <c r="C295" s="5" t="s">
-        <v>314</v>
+        <v>454</v>
       </c>
       <c r="D295" s="3">
         <v>1</v>
@@ -4895,7 +4964,7 @@
       <c r="A296" s="2"/>
       <c r="B296" s="2"/>
       <c r="C296" s="5" t="s">
-        <v>315</v>
+        <v>455</v>
       </c>
       <c r="D296" s="3">
         <v>1</v>
@@ -4903,33 +4972,31 @@
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" s="2"/>
-      <c r="B297" s="2"/>
-      <c r="C297" s="7" t="s">
-        <v>316</v>
+      <c r="B297" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C297" s="5" t="s">
+        <v>300</v>
       </c>
       <c r="D297" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" s="2"/>
       <c r="B298" s="2"/>
       <c r="C298" s="5" t="s">
-        <v>402</v>
+        <v>301</v>
       </c>
       <c r="D298" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A299" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="B299" s="2" t="s">
-        <v>414</v>
-      </c>
+      <c r="A299" s="2"/>
+      <c r="B299" s="2"/>
       <c r="C299" s="5" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="D299" s="3">
         <v>1</v>
@@ -4939,7 +5006,7 @@
       <c r="A300" s="2"/>
       <c r="B300" s="2"/>
       <c r="C300" s="5" t="s">
-        <v>318</v>
+        <v>456</v>
       </c>
       <c r="D300" s="3">
         <v>1</v>
@@ -4949,7 +5016,7 @@
       <c r="A301" s="2"/>
       <c r="B301" s="2"/>
       <c r="C301" s="5" t="s">
-        <v>319</v>
+        <v>457</v>
       </c>
       <c r="D301" s="3">
         <v>1</v>
@@ -4957,9 +5024,11 @@
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" s="2"/>
-      <c r="B302" s="2"/>
+      <c r="B302" s="2" t="s">
+        <v>309</v>
+      </c>
       <c r="C302" s="5" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="D302" s="3">
         <v>1</v>
@@ -4969,7 +5038,7 @@
       <c r="A303" s="2"/>
       <c r="B303" s="2"/>
       <c r="C303" s="5" t="s">
-        <v>321</v>
+        <v>304</v>
       </c>
       <c r="D303" s="3">
         <v>1</v>
@@ -4979,7 +5048,7 @@
       <c r="A304" s="2"/>
       <c r="B304" s="2"/>
       <c r="C304" s="5" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="D304" s="3">
         <v>1</v>
@@ -4989,7 +5058,7 @@
       <c r="A305" s="2"/>
       <c r="B305" s="2"/>
       <c r="C305" s="5" t="s">
-        <v>323</v>
+        <v>458</v>
       </c>
       <c r="D305" s="3">
         <v>1</v>
@@ -4999,7 +5068,7 @@
       <c r="A306" s="2"/>
       <c r="B306" s="2"/>
       <c r="C306" s="5" t="s">
-        <v>324</v>
+        <v>459</v>
       </c>
       <c r="D306" s="3">
         <v>1</v>
@@ -5007,9 +5076,11 @@
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" s="2"/>
-      <c r="B307" s="2"/>
+      <c r="B307" s="2" t="s">
+        <v>312</v>
+      </c>
       <c r="C307" s="5" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="D307" s="3">
         <v>1</v>
@@ -5017,11 +5088,9 @@
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" s="2"/>
-      <c r="B308" s="2" t="s">
-        <v>364</v>
-      </c>
+      <c r="B308" s="2"/>
       <c r="C308" s="5" t="s">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="D308" s="3">
         <v>1</v>
@@ -5029,19 +5098,23 @@
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" s="2"/>
-      <c r="B309" s="2"/>
+      <c r="B309" s="2" t="s">
+        <v>460</v>
+      </c>
       <c r="C309" s="5" t="s">
-        <v>327</v>
+        <v>461</v>
       </c>
       <c r="D309" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A310" s="2"/>
+      <c r="A310" s="2" t="s">
+        <v>313</v>
+      </c>
       <c r="B310" s="2"/>
       <c r="C310" s="5" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="D310" s="3">
         <v>1</v>
@@ -5051,7 +5124,7 @@
       <c r="A311" s="2"/>
       <c r="B311" s="2"/>
       <c r="C311" s="5" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="D311" s="3">
         <v>1</v>
@@ -5060,28 +5133,32 @@
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" s="2"/>
       <c r="B312" s="2"/>
-      <c r="C312" s="5" t="s">
-        <v>330</v>
+      <c r="C312" s="7" t="s">
+        <v>316</v>
       </c>
       <c r="D312" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" s="2"/>
       <c r="B313" s="2"/>
       <c r="C313" s="5" t="s">
-        <v>331</v>
+        <v>402</v>
       </c>
       <c r="D313" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A314" s="2"/>
-      <c r="B314" s="2"/>
+      <c r="A314" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B314" s="2" t="s">
+        <v>414</v>
+      </c>
       <c r="C314" s="5" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="D314" s="3">
         <v>1</v>
@@ -5091,7 +5168,7 @@
       <c r="A315" s="2"/>
       <c r="B315" s="2"/>
       <c r="C315" s="5" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="D315" s="3">
         <v>1</v>
@@ -5101,7 +5178,7 @@
       <c r="A316" s="2"/>
       <c r="B316" s="2"/>
       <c r="C316" s="5" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="D316" s="3">
         <v>1</v>
@@ -5111,7 +5188,7 @@
       <c r="A317" s="2"/>
       <c r="B317" s="2"/>
       <c r="C317" s="5" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="D317" s="3">
         <v>1</v>
@@ -5121,7 +5198,7 @@
       <c r="A318" s="2"/>
       <c r="B318" s="2"/>
       <c r="C318" s="5" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="D318" s="3">
         <v>1</v>
@@ -5131,7 +5208,7 @@
       <c r="A319" s="2"/>
       <c r="B319" s="2"/>
       <c r="C319" s="5" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="D319" s="3">
         <v>1</v>
@@ -5141,7 +5218,7 @@
       <c r="A320" s="2"/>
       <c r="B320" s="2"/>
       <c r="C320" s="5" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="D320" s="3">
         <v>1</v>
@@ -5151,7 +5228,7 @@
       <c r="A321" s="2"/>
       <c r="B321" s="2"/>
       <c r="C321" s="5" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="D321" s="3">
         <v>1</v>
@@ -5161,7 +5238,7 @@
       <c r="A322" s="2"/>
       <c r="B322" s="2"/>
       <c r="C322" s="5" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="D322" s="3">
         <v>1</v>
@@ -5169,9 +5246,11 @@
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" s="2"/>
-      <c r="B323" s="2"/>
+      <c r="B323" s="2" t="s">
+        <v>364</v>
+      </c>
       <c r="C323" s="5" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="D323" s="3">
         <v>1</v>
@@ -5181,7 +5260,7 @@
       <c r="A324" s="2"/>
       <c r="B324" s="2"/>
       <c r="C324" s="5" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="D324" s="3">
         <v>1</v>
@@ -5191,7 +5270,7 @@
       <c r="A325" s="2"/>
       <c r="B325" s="2"/>
       <c r="C325" s="5" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="D325" s="3">
         <v>1</v>
@@ -5201,7 +5280,7 @@
       <c r="A326" s="2"/>
       <c r="B326" s="2"/>
       <c r="C326" s="5" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="D326" s="3">
         <v>1</v>
@@ -5211,7 +5290,7 @@
       <c r="A327" s="2"/>
       <c r="B327" s="2"/>
       <c r="C327" s="5" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="D327" s="3">
         <v>1</v>
@@ -5221,7 +5300,7 @@
       <c r="A328" s="2"/>
       <c r="B328" s="2"/>
       <c r="C328" s="5" t="s">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="D328" s="3">
         <v>1</v>
@@ -5231,7 +5310,7 @@
       <c r="A329" s="2"/>
       <c r="B329" s="2"/>
       <c r="C329" s="5" t="s">
-        <v>361</v>
+        <v>332</v>
       </c>
       <c r="D329" s="3">
         <v>1</v>
@@ -5241,7 +5320,7 @@
       <c r="A330" s="2"/>
       <c r="B330" s="2"/>
       <c r="C330" s="5" t="s">
-        <v>362</v>
+        <v>333</v>
       </c>
       <c r="D330" s="3">
         <v>1</v>
@@ -5251,21 +5330,17 @@
       <c r="A331" s="2"/>
       <c r="B331" s="2"/>
       <c r="C331" s="5" t="s">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="D331" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A332" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="B332" s="2" t="s">
-        <v>415</v>
-      </c>
+      <c r="A332" s="2"/>
+      <c r="B332" s="2"/>
       <c r="C332" s="5" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="D332" s="3">
         <v>1</v>
@@ -5275,7 +5350,7 @@
       <c r="A333" s="2"/>
       <c r="B333" s="2"/>
       <c r="C333" s="5" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="D333" s="3">
         <v>1</v>
@@ -5285,7 +5360,7 @@
       <c r="A334" s="2"/>
       <c r="B334" s="2"/>
       <c r="C334" s="5" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="D334" s="3">
         <v>1</v>
@@ -5295,7 +5370,7 @@
       <c r="A335" s="2"/>
       <c r="B335" s="2"/>
       <c r="C335" s="5" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="D335" s="3">
         <v>1</v>
@@ -5305,7 +5380,7 @@
       <c r="A336" s="2"/>
       <c r="B336" s="2"/>
       <c r="C336" s="5" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="D336" s="3">
         <v>1</v>
@@ -5315,7 +5390,7 @@
       <c r="A337" s="2"/>
       <c r="B337" s="2"/>
       <c r="C337" s="5" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="D337" s="3">
         <v>1</v>
@@ -5325,7 +5400,7 @@
       <c r="A338" s="2"/>
       <c r="B338" s="2"/>
       <c r="C338" s="5" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="D338" s="3">
         <v>1</v>
@@ -5335,7 +5410,7 @@
       <c r="A339" s="2"/>
       <c r="B339" s="2"/>
       <c r="C339" s="5" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="D339" s="3">
         <v>1</v>
@@ -5345,7 +5420,7 @@
       <c r="A340" s="2"/>
       <c r="B340" s="2"/>
       <c r="C340" s="5" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="D340" s="3">
         <v>1</v>
@@ -5355,7 +5430,7 @@
       <c r="A341" s="2"/>
       <c r="B341" s="2"/>
       <c r="C341" s="5" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="D341" s="3">
         <v>1</v>
@@ -5365,7 +5440,7 @@
       <c r="A342" s="2"/>
       <c r="B342" s="2"/>
       <c r="C342" s="5" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="D342" s="3">
         <v>1</v>
@@ -5375,7 +5450,7 @@
       <c r="A343" s="2"/>
       <c r="B343" s="2"/>
       <c r="C343" s="5" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D343" s="3">
         <v>1</v>
@@ -5383,11 +5458,9 @@
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344" s="2"/>
-      <c r="B344" s="2" t="s">
-        <v>365</v>
-      </c>
+      <c r="B344" s="2"/>
       <c r="C344" s="5" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="D344" s="3">
         <v>1</v>
@@ -5397,7 +5470,7 @@
       <c r="A345" s="2"/>
       <c r="B345" s="2"/>
       <c r="C345" s="5" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="D345" s="3">
         <v>1</v>
@@ -5407,17 +5480,21 @@
       <c r="A346" s="2"/>
       <c r="B346" s="2"/>
       <c r="C346" s="5" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="D346" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A347" s="2"/>
-      <c r="B347" s="2"/>
+      <c r="A347" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B347" s="2" t="s">
+        <v>415</v>
+      </c>
       <c r="C347" s="5" t="s">
-        <v>369</v>
+        <v>348</v>
       </c>
       <c r="D347" s="3">
         <v>1</v>
@@ -5427,7 +5504,7 @@
       <c r="A348" s="2"/>
       <c r="B348" s="2"/>
       <c r="C348" s="5" t="s">
-        <v>370</v>
+        <v>349</v>
       </c>
       <c r="D348" s="3">
         <v>1</v>
@@ -5437,7 +5514,7 @@
       <c r="A349" s="2"/>
       <c r="B349" s="2"/>
       <c r="C349" s="5" t="s">
-        <v>371</v>
+        <v>350</v>
       </c>
       <c r="D349" s="3">
         <v>1</v>
@@ -5447,7 +5524,7 @@
       <c r="A350" s="2"/>
       <c r="B350" s="2"/>
       <c r="C350" s="5" t="s">
-        <v>372</v>
+        <v>351</v>
       </c>
       <c r="D350" s="3">
         <v>1</v>
@@ -5457,7 +5534,7 @@
       <c r="A351" s="2"/>
       <c r="B351" s="2"/>
       <c r="C351" s="5" t="s">
-        <v>373</v>
+        <v>352</v>
       </c>
       <c r="D351" s="3">
         <v>1</v>
@@ -5467,7 +5544,7 @@
       <c r="A352" s="2"/>
       <c r="B352" s="2"/>
       <c r="C352" s="5" t="s">
-        <v>374</v>
+        <v>353</v>
       </c>
       <c r="D352" s="3">
         <v>1</v>
@@ -5477,7 +5554,7 @@
       <c r="A353" s="2"/>
       <c r="B353" s="2"/>
       <c r="C353" s="5" t="s">
-        <v>375</v>
+        <v>354</v>
       </c>
       <c r="D353" s="3">
         <v>1</v>
@@ -5487,7 +5564,7 @@
       <c r="A354" s="2"/>
       <c r="B354" s="2"/>
       <c r="C354" s="5" t="s">
-        <v>376</v>
+        <v>355</v>
       </c>
       <c r="D354" s="3">
         <v>1</v>
@@ -5497,21 +5574,17 @@
       <c r="A355" s="2"/>
       <c r="B355" s="2"/>
       <c r="C355" s="5" t="s">
-        <v>377</v>
+        <v>356</v>
       </c>
       <c r="D355" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A356" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="B356" s="2" t="s">
-        <v>416</v>
-      </c>
+      <c r="A356" s="2"/>
+      <c r="B356" s="2"/>
       <c r="C356" s="5" t="s">
-        <v>379</v>
+        <v>357</v>
       </c>
       <c r="D356" s="3">
         <v>1</v>
@@ -5521,7 +5594,7 @@
       <c r="A357" s="2"/>
       <c r="B357" s="2"/>
       <c r="C357" s="5" t="s">
-        <v>380</v>
+        <v>358</v>
       </c>
       <c r="D357" s="3">
         <v>1</v>
@@ -5531,7 +5604,7 @@
       <c r="A358" s="2"/>
       <c r="B358" s="2"/>
       <c r="C358" s="5" t="s">
-        <v>381</v>
+        <v>359</v>
       </c>
       <c r="D358" s="3">
         <v>1</v>
@@ -5539,9 +5612,11 @@
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A359" s="2"/>
-      <c r="B359" s="2"/>
+      <c r="B359" s="2" t="s">
+        <v>365</v>
+      </c>
       <c r="C359" s="5" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="D359" s="3">
         <v>1</v>
@@ -5551,7 +5626,7 @@
       <c r="A360" s="2"/>
       <c r="B360" s="2"/>
       <c r="C360" s="5" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
       <c r="D360" s="3">
         <v>1</v>
@@ -5561,7 +5636,7 @@
       <c r="A361" s="2"/>
       <c r="B361" s="2"/>
       <c r="C361" s="5" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
       <c r="D361" s="3">
         <v>1</v>
@@ -5571,7 +5646,7 @@
       <c r="A362" s="2"/>
       <c r="B362" s="2"/>
       <c r="C362" s="5" t="s">
-        <v>385</v>
+        <v>369</v>
       </c>
       <c r="D362" s="3">
         <v>1</v>
@@ -5581,7 +5656,7 @@
       <c r="A363" s="2"/>
       <c r="B363" s="2"/>
       <c r="C363" s="5" t="s">
-        <v>386</v>
+        <v>370</v>
       </c>
       <c r="D363" s="3">
         <v>1</v>
@@ -5589,11 +5664,9 @@
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A364" s="2"/>
-      <c r="B364" s="2" t="s">
-        <v>387</v>
-      </c>
+      <c r="B364" s="2"/>
       <c r="C364" s="5" t="s">
-        <v>388</v>
+        <v>371</v>
       </c>
       <c r="D364" s="3">
         <v>1</v>
@@ -5603,7 +5676,7 @@
       <c r="A365" s="2"/>
       <c r="B365" s="2"/>
       <c r="C365" s="5" t="s">
-        <v>389</v>
+        <v>372</v>
       </c>
       <c r="D365" s="3">
         <v>1</v>
@@ -5613,7 +5686,7 @@
       <c r="A366" s="2"/>
       <c r="B366" s="2"/>
       <c r="C366" s="5" t="s">
-        <v>390</v>
+        <v>373</v>
       </c>
       <c r="D366" s="3">
         <v>1</v>
@@ -5623,7 +5696,7 @@
       <c r="A367" s="2"/>
       <c r="B367" s="2"/>
       <c r="C367" s="5" t="s">
-        <v>391</v>
+        <v>374</v>
       </c>
       <c r="D367" s="3">
         <v>1</v>
@@ -5633,7 +5706,7 @@
       <c r="A368" s="2"/>
       <c r="B368" s="2"/>
       <c r="C368" s="5" t="s">
-        <v>421</v>
+        <v>375</v>
       </c>
       <c r="D368" s="3">
         <v>1</v>
@@ -5643,7 +5716,7 @@
       <c r="A369" s="2"/>
       <c r="B369" s="2"/>
       <c r="C369" s="5" t="s">
-        <v>422</v>
+        <v>376</v>
       </c>
       <c r="D369" s="3">
         <v>1</v>
@@ -5653,29 +5726,31 @@
       <c r="A370" s="2"/>
       <c r="B370" s="2"/>
       <c r="C370" s="5" t="s">
-        <v>448</v>
+        <v>377</v>
       </c>
       <c r="D370" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A371" s="2"/>
-      <c r="B371" s="2"/>
+      <c r="A371" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B371" s="2" t="s">
+        <v>416</v>
+      </c>
       <c r="C371" s="5" t="s">
-        <v>449</v>
+        <v>379</v>
       </c>
       <c r="D371" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A372" s="2" t="s">
-        <v>450</v>
-      </c>
+      <c r="A372" s="2"/>
       <c r="B372" s="2"/>
       <c r="C372" s="5" t="s">
-        <v>451</v>
+        <v>380</v>
       </c>
       <c r="D372" s="3">
         <v>1</v>
@@ -5685,7 +5760,7 @@
       <c r="A373" s="2"/>
       <c r="B373" s="2"/>
       <c r="C373" s="5" t="s">
-        <v>452</v>
+        <v>381</v>
       </c>
       <c r="D373" s="3">
         <v>1</v>
@@ -5695,19 +5770,17 @@
       <c r="A374" s="2"/>
       <c r="B374" s="2"/>
       <c r="C374" s="5" t="s">
-        <v>453</v>
+        <v>382</v>
       </c>
       <c r="D374" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A375" s="2" t="s">
-        <v>392</v>
-      </c>
+      <c r="A375" s="2"/>
       <c r="B375" s="2"/>
       <c r="C375" s="5" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="D375" s="3">
         <v>1</v>
@@ -5717,7 +5790,7 @@
       <c r="A376" s="2"/>
       <c r="B376" s="2"/>
       <c r="C376" s="5" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="D376" s="3">
         <v>1</v>
@@ -5727,7 +5800,7 @@
       <c r="A377" s="2"/>
       <c r="B377" s="2"/>
       <c r="C377" s="5" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="D377" s="3">
         <v>1</v>
@@ -5737,7 +5810,7 @@
       <c r="A378" s="2"/>
       <c r="B378" s="2"/>
       <c r="C378" s="5" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="D378" s="3">
         <v>1</v>
@@ -5745,9 +5818,11 @@
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A379" s="2"/>
-      <c r="B379" s="2"/>
+      <c r="B379" s="2" t="s">
+        <v>387</v>
+      </c>
       <c r="C379" s="5" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="D379" s="3">
         <v>1</v>
@@ -5757,19 +5832,17 @@
       <c r="A380" s="2"/>
       <c r="B380" s="2"/>
       <c r="C380" s="5" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="D380" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A381" s="2" t="s">
-        <v>129</v>
-      </c>
+      <c r="A381" s="2"/>
       <c r="B381" s="2"/>
       <c r="C381" s="5" t="s">
-        <v>130</v>
+        <v>390</v>
       </c>
       <c r="D381" s="3">
         <v>1</v>
@@ -5779,7 +5852,7 @@
       <c r="A382" s="2"/>
       <c r="B382" s="2"/>
       <c r="C382" s="5" t="s">
-        <v>131</v>
+        <v>391</v>
       </c>
       <c r="D382" s="3">
         <v>1</v>
@@ -5789,7 +5862,7 @@
       <c r="A383" s="2"/>
       <c r="B383" s="2"/>
       <c r="C383" s="5" t="s">
-        <v>132</v>
+        <v>421</v>
       </c>
       <c r="D383" s="3">
         <v>1</v>
@@ -5799,7 +5872,7 @@
       <c r="A384" s="2"/>
       <c r="B384" s="2"/>
       <c r="C384" s="5" t="s">
-        <v>133</v>
+        <v>422</v>
       </c>
       <c r="D384" s="3">
         <v>1</v>
@@ -5808,92 +5881,158 @@
     <row r="385" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A385" s="2"/>
       <c r="B385" s="2"/>
-      <c r="C385" s="7"/>
-      <c r="D385" s="3"/>
+      <c r="C385" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="D385" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A386" s="2"/>
       <c r="B386" s="2"/>
-      <c r="C386" s="7"/>
-      <c r="D386" s="3"/>
+      <c r="C386" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="D386" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A387" s="2"/>
+      <c r="A387" s="2" t="s">
+        <v>440</v>
+      </c>
       <c r="B387" s="2"/>
-      <c r="C387" s="7"/>
-      <c r="D387" s="3"/>
+      <c r="C387" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="D387" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A388" s="2"/>
       <c r="B388" s="2"/>
-      <c r="C388" s="7"/>
-      <c r="D388" s="3"/>
+      <c r="C388" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="D388" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A389" s="2"/>
       <c r="B389" s="2"/>
-      <c r="C389" s="7"/>
-      <c r="D389" s="3"/>
+      <c r="C389" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="D389" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A390" s="2"/>
+      <c r="A390" s="2" t="s">
+        <v>392</v>
+      </c>
       <c r="B390" s="2"/>
-      <c r="C390" s="7"/>
-      <c r="D390" s="3"/>
+      <c r="C390" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="D390" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A391" s="2"/>
       <c r="B391" s="2"/>
-      <c r="C391" s="7"/>
-      <c r="D391" s="3"/>
+      <c r="C391" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="D391" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A392" s="2"/>
       <c r="B392" s="2"/>
-      <c r="C392" s="7"/>
-      <c r="D392" s="3"/>
+      <c r="C392" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="D392" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A393" s="2"/>
       <c r="B393" s="2"/>
-      <c r="C393" s="7"/>
-      <c r="D393" s="3"/>
+      <c r="C393" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="D393" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A394" s="2"/>
       <c r="B394" s="2"/>
-      <c r="C394" s="7"/>
-      <c r="D394" s="3"/>
+      <c r="C394" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="D394" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A395" s="2"/>
       <c r="B395" s="2"/>
-      <c r="C395" s="7"/>
-      <c r="D395" s="3"/>
+      <c r="C395" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="D395" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A396" s="2"/>
+      <c r="A396" s="2" t="s">
+        <v>129</v>
+      </c>
       <c r="B396" s="2"/>
-      <c r="C396" s="7"/>
-      <c r="D396" s="3"/>
+      <c r="C396" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D396" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A397" s="2"/>
       <c r="B397" s="2"/>
-      <c r="C397" s="7"/>
-      <c r="D397" s="3"/>
+      <c r="C397" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D397" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A398" s="2"/>
       <c r="B398" s="2"/>
-      <c r="C398" s="7"/>
-      <c r="D398" s="3"/>
+      <c r="C398" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D398" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A399" s="2"/>
       <c r="B399" s="2"/>
-      <c r="C399" s="7"/>
-      <c r="D399" s="3"/>
+      <c r="C399" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D399" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A400" s="2"/>
@@ -5945,7 +6084,7 @@
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A408" s="2"/>
-      <c r="B408" s="5"/>
+      <c r="B408" s="2"/>
       <c r="C408" s="7"/>
       <c r="D408" s="3"/>
     </row>
@@ -5964,111 +6103,169 @@
     <row r="411" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A411" s="2"/>
       <c r="B411" s="2"/>
-      <c r="C411" s="5"/>
+      <c r="C411" s="7"/>
       <c r="D411" s="3"/>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A412" s="2"/>
       <c r="B412" s="2"/>
-      <c r="C412" s="5"/>
+      <c r="C412" s="7"/>
       <c r="D412" s="3"/>
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A413" s="2"/>
       <c r="B413" s="2"/>
-      <c r="C413" s="5"/>
+      <c r="C413" s="7"/>
       <c r="D413" s="3"/>
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A414" s="2"/>
       <c r="B414" s="2"/>
-      <c r="C414" s="5"/>
+      <c r="C414" s="7"/>
       <c r="D414" s="3"/>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A415" s="2"/>
       <c r="B415" s="2"/>
-      <c r="C415" s="2"/>
+      <c r="C415" s="7"/>
       <c r="D415" s="3"/>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A416" s="2"/>
       <c r="B416" s="2"/>
-      <c r="C416" s="2"/>
+      <c r="C416" s="7"/>
       <c r="D416" s="3"/>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A417" s="2"/>
       <c r="B417" s="2"/>
-      <c r="C417" s="2"/>
+      <c r="C417" s="7"/>
       <c r="D417" s="3"/>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A418" s="2"/>
       <c r="B418" s="2"/>
-      <c r="C418" s="2"/>
+      <c r="C418" s="7"/>
       <c r="D418" s="3"/>
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A419" s="2"/>
       <c r="B419" s="2"/>
-      <c r="C419" s="2"/>
+      <c r="C419" s="7"/>
       <c r="D419" s="3"/>
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A420" s="2"/>
       <c r="B420" s="2"/>
-      <c r="C420" s="2"/>
+      <c r="C420" s="7"/>
       <c r="D420" s="3"/>
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A421" s="2"/>
       <c r="B421" s="2"/>
-      <c r="C421" s="2"/>
+      <c r="C421" s="7"/>
       <c r="D421" s="3"/>
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A422" s="2"/>
       <c r="B422" s="2"/>
-      <c r="C422" s="2"/>
+      <c r="C422" s="7"/>
       <c r="D422" s="3"/>
     </row>
-    <row r="433" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="434" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="435" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="436" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="437" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="438" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="439" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="440" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="441" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="442" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="443" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="444" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="445" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="446" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="447" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="448" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="449" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="450" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="451" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="452" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="453" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="454" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="455" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="456" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="457" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="458" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="459" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="460" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="461" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="462" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="463" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="464" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A423" s="2"/>
+      <c r="B423" s="5"/>
+      <c r="C423" s="7"/>
+      <c r="D423" s="3"/>
+    </row>
+    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A424" s="2"/>
+      <c r="B424" s="2"/>
+      <c r="C424" s="7"/>
+      <c r="D424" s="3"/>
+    </row>
+    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A425" s="2"/>
+      <c r="B425" s="2"/>
+      <c r="C425" s="7"/>
+      <c r="D425" s="3"/>
+    </row>
+    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A426" s="2"/>
+      <c r="B426" s="2"/>
+      <c r="C426" s="5"/>
+      <c r="D426" s="3"/>
+    </row>
+    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A427" s="2"/>
+      <c r="B427" s="2"/>
+      <c r="C427" s="5"/>
+      <c r="D427" s="3"/>
+    </row>
+    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A428" s="2"/>
+      <c r="B428" s="2"/>
+      <c r="C428" s="5"/>
+      <c r="D428" s="3"/>
+    </row>
+    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A429" s="2"/>
+      <c r="B429" s="2"/>
+      <c r="C429" s="5"/>
+      <c r="D429" s="3"/>
+    </row>
+    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A430" s="2"/>
+      <c r="B430" s="2"/>
+      <c r="C430" s="2"/>
+      <c r="D430" s="3"/>
+    </row>
+    <row r="431" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A431" s="2"/>
+      <c r="B431" s="2"/>
+      <c r="C431" s="2"/>
+      <c r="D431" s="3"/>
+    </row>
+    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A432" s="2"/>
+      <c r="B432" s="2"/>
+      <c r="C432" s="2"/>
+      <c r="D432" s="3"/>
+    </row>
+    <row r="433" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A433" s="2"/>
+      <c r="B433" s="2"/>
+      <c r="C433" s="2"/>
+      <c r="D433" s="3"/>
+    </row>
+    <row r="434" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A434" s="2"/>
+      <c r="B434" s="2"/>
+      <c r="C434" s="2"/>
+      <c r="D434" s="3"/>
+    </row>
+    <row r="435" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A435" s="2"/>
+      <c r="B435" s="2"/>
+      <c r="C435" s="2"/>
+      <c r="D435" s="3"/>
+    </row>
+    <row r="436" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A436" s="2"/>
+      <c r="B436" s="2"/>
+      <c r="C436" s="2"/>
+      <c r="D436" s="3"/>
+    </row>
+    <row r="437" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A437" s="2"/>
+      <c r="B437" s="2"/>
+      <c r="C437" s="2"/>
+      <c r="D437" s="3"/>
+    </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="C11:C12" name="Tags_1_3_1"/>
-    <protectedRange sqref="C16" name="Tags_1_3_1_3"/>
+    <protectedRange sqref="C15:C16" name="Tags_1_3_1"/>
+    <protectedRange sqref="C20" name="Tags_1_3_1_3"/>
   </protectedRanges>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6076,7 +6273,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE4981EB-4941-4E69-A8D1-C9949FF3C2A8}">
-  <dimension ref="A1:D464"/>
+  <dimension ref="A1:D430"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.7109375" customWidth="1"/>
@@ -6101,7 +6298,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>411</v>
@@ -6137,7 +6334,7 @@
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="5" t="s">
-        <v>73</v>
+        <v>473</v>
       </c>
       <c r="D5" s="6">
         <v>1</v>
@@ -6147,7 +6344,7 @@
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="5" t="s">
-        <v>74</v>
+        <v>474</v>
       </c>
       <c r="D6" s="6">
         <v>1</v>
@@ -6157,7 +6354,7 @@
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D7" s="6">
         <v>1</v>
@@ -6167,7 +6364,7 @@
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="5" t="s">
-        <v>419</v>
+        <v>74</v>
       </c>
       <c r="D8" s="6">
         <v>1</v>
@@ -6177,7 +6374,7 @@
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="5" t="s">
-        <v>420</v>
+        <v>75</v>
       </c>
       <c r="D9" s="6">
         <v>1</v>
@@ -6187,61 +6384,59 @@
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="D10" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="D11" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="D12" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="D13" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D14" s="6">
         <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="3">
-        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
+      <c r="B15" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="C15" s="5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D15" s="3">
         <v>1</v>
@@ -6251,7 +6446,7 @@
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D16" s="3">
         <v>1</v>
@@ -6259,11 +6454,9 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
-      <c r="B17" s="2" t="s">
-        <v>33</v>
-      </c>
+      <c r="B17" s="2"/>
       <c r="C17" s="5" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D17" s="3">
         <v>1</v>
@@ -6271,9 +6464,11 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
+      <c r="B18" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="C18" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D18" s="3">
         <v>1</v>
@@ -6283,7 +6478,7 @@
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="5" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D19" s="3">
         <v>1</v>
@@ -6291,11 +6486,9 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
-      <c r="B20" s="2" t="s">
-        <v>34</v>
-      </c>
+      <c r="B20" s="2"/>
       <c r="C20" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D20" s="3">
         <v>1</v>
@@ -6303,9 +6496,11 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
+      <c r="B21" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="C21" s="5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D21" s="3">
         <v>1</v>
@@ -6315,7 +6510,7 @@
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D22" s="3">
         <v>1</v>
@@ -6323,11 +6518,9 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
-      <c r="B23" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="B23" s="2"/>
       <c r="C23" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D23" s="3">
         <v>1</v>
@@ -6335,9 +6528,11 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
+      <c r="B24" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="C24" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D24" s="3">
         <v>1</v>
@@ -6347,7 +6542,7 @@
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D25" s="3">
         <v>1</v>
@@ -6355,11 +6550,9 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
-      <c r="B26" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="B26" s="2"/>
       <c r="C26" s="5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D26" s="3">
         <v>1</v>
@@ -6367,9 +6560,11 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
+      <c r="B27" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="C27" s="5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D27" s="3">
         <v>1</v>
@@ -6379,7 +6574,7 @@
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D28" s="3">
         <v>1</v>
@@ -6387,11 +6582,9 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
-      <c r="B29" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="B29" s="2"/>
       <c r="C29" s="5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D29" s="3">
         <v>1</v>
@@ -6399,9 +6592,11 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
+      <c r="B30" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="C30" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D30" s="3">
         <v>1</v>
@@ -6411,7 +6606,7 @@
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="5" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D31" s="3">
         <v>1</v>
@@ -6419,11 +6614,9 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
-      <c r="B32" s="2" t="s">
-        <v>38</v>
-      </c>
+      <c r="B32" s="2"/>
       <c r="C32" s="5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D32" s="3">
         <v>1</v>
@@ -6431,9 +6624,11 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
+      <c r="B33" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="C33" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D33" s="3">
         <v>1</v>
@@ -6443,7 +6638,7 @@
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D34" s="3">
         <v>1</v>
@@ -6451,11 +6646,9 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
-      <c r="B35" s="2" t="s">
-        <v>39</v>
-      </c>
+      <c r="B35" s="2"/>
       <c r="C35" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D35" s="3">
         <v>1</v>
@@ -6463,9 +6656,11 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
+      <c r="B36" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="C36" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D36" s="3">
         <v>1</v>
@@ -6475,7 +6670,7 @@
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="5" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D37" s="3">
         <v>1</v>
@@ -6483,11 +6678,9 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
-      <c r="B38" s="2" t="s">
-        <v>40</v>
-      </c>
+      <c r="B38" s="2"/>
       <c r="C38" s="5" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="D38" s="3">
         <v>1</v>
@@ -6495,9 +6688,11 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
+      <c r="B39" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="C39" s="5" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D39" s="3">
         <v>1</v>
@@ -6505,11 +6700,9 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
-      <c r="B40" s="2" t="s">
-        <v>57</v>
-      </c>
+      <c r="B40" s="2"/>
       <c r="C40" s="5" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D40" s="3">
         <v>1</v>
@@ -6519,7 +6712,7 @@
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="5" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D41" s="3">
         <v>1</v>
@@ -6528,10 +6721,10 @@
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2" t="s">
-        <v>58</v>
+        <v>447</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>45</v>
+        <v>448</v>
       </c>
       <c r="D42" s="3">
         <v>1</v>
@@ -6541,7 +6734,7 @@
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="5" t="s">
-        <v>46</v>
+        <v>449</v>
       </c>
       <c r="D43" s="3">
         <v>1</v>
@@ -6550,10 +6743,10 @@
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D44" s="3">
         <v>1</v>
@@ -6563,7 +6756,7 @@
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="5" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D45" s="3">
         <v>1</v>
@@ -6572,10 +6765,10 @@
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D46" s="3">
         <v>1</v>
@@ -6585,7 +6778,7 @@
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="5" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D47" s="3">
         <v>1</v>
@@ -6594,10 +6787,10 @@
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D48" s="3">
         <v>1</v>
@@ -6607,7 +6800,7 @@
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="5" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D49" s="3">
         <v>1</v>
@@ -6616,10 +6809,10 @@
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D50" s="3">
         <v>1</v>
@@ -6629,7 +6822,7 @@
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="5" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D51" s="3">
         <v>1</v>
@@ -6638,10 +6831,10 @@
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D52" s="3">
         <v>1</v>
@@ -6651,7 +6844,7 @@
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D53" s="3">
         <v>1</v>
@@ -6660,10 +6853,10 @@
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D54" s="3">
         <v>1</v>
@@ -6673,7 +6866,7 @@
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D55" s="3">
         <v>1</v>
@@ -6682,10 +6875,10 @@
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="D56" s="3">
         <v>1</v>
@@ -6695,7 +6888,7 @@
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="5" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="D57" s="3">
         <v>1</v>
@@ -6703,9 +6896,11 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
-      <c r="B58" s="2"/>
+      <c r="B58" s="2" t="s">
+        <v>63</v>
+      </c>
       <c r="C58" s="5" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="D58" s="3">
         <v>1</v>
@@ -6715,7 +6910,7 @@
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="5" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="D59" s="3">
         <v>1</v>
@@ -6724,10 +6919,10 @@
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="2" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>76</v>
+        <v>445</v>
       </c>
       <c r="D60" s="3">
         <v>1</v>
@@ -6737,7 +6932,7 @@
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="5" t="s">
-        <v>77</v>
+        <v>446</v>
       </c>
       <c r="D61" s="3">
         <v>1</v>
@@ -6745,9 +6940,11 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
-      <c r="B62" s="2"/>
+      <c r="B62" s="2" t="s">
+        <v>464</v>
+      </c>
       <c r="C62" s="5" t="s">
-        <v>78</v>
+        <v>467</v>
       </c>
       <c r="D62" s="3">
         <v>1</v>
@@ -6757,7 +6954,7 @@
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="5" t="s">
-        <v>79</v>
+        <v>472</v>
       </c>
       <c r="D63" s="3">
         <v>1</v>
@@ -6765,9 +6962,11 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
-      <c r="B64" s="2"/>
+      <c r="B64" s="2" t="s">
+        <v>465</v>
+      </c>
       <c r="C64" s="5" t="s">
-        <v>80</v>
+        <v>468</v>
       </c>
       <c r="D64" s="3">
         <v>1</v>
@@ -6777,7 +6976,7 @@
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="5" t="s">
-        <v>81</v>
+        <v>471</v>
       </c>
       <c r="D65" s="3">
         <v>1</v>
@@ -6785,9 +6984,11 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
-      <c r="B66" s="2"/>
+      <c r="B66" s="2" t="s">
+        <v>466</v>
+      </c>
       <c r="C66" s="5" t="s">
-        <v>82</v>
+        <v>469</v>
       </c>
       <c r="D66" s="3">
         <v>1</v>
@@ -6797,7 +6998,7 @@
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="5" t="s">
-        <v>83</v>
+        <v>470</v>
       </c>
       <c r="D67" s="3">
         <v>1</v>
@@ -6805,9 +7006,11 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
-      <c r="B68" s="2"/>
+      <c r="B68" s="2" t="s">
+        <v>65</v>
+      </c>
       <c r="C68" s="5" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="D68" s="3">
         <v>1</v>
@@ -6817,19 +7020,17 @@
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="5" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="D69" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="2" t="s">
-        <v>87</v>
-      </c>
+      <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="5" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="D70" s="3">
         <v>1</v>
@@ -6839,7 +7040,7 @@
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="5" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="D71" s="3">
         <v>1</v>
@@ -6847,9 +7048,11 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
-      <c r="B72" s="2"/>
+      <c r="B72" s="2" t="s">
+        <v>86</v>
+      </c>
       <c r="C72" s="5" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="D72" s="3">
         <v>1</v>
@@ -6859,7 +7062,7 @@
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="5" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="D73" s="3">
         <v>1</v>
@@ -6869,7 +7072,7 @@
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="5" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="D74" s="3">
         <v>1</v>
@@ -6879,7 +7082,7 @@
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="5" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="D75" s="3">
         <v>1</v>
@@ -6889,7 +7092,7 @@
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="5" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="D76" s="3">
         <v>1</v>
@@ -6899,7 +7102,7 @@
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="5" t="s">
-        <v>434</v>
+        <v>81</v>
       </c>
       <c r="D77" s="3">
         <v>1</v>
@@ -6909,7 +7112,7 @@
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="5" t="s">
-        <v>435</v>
+        <v>82</v>
       </c>
       <c r="D78" s="3">
         <v>1</v>
@@ -6919,19 +7122,17 @@
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="5" t="s">
-        <v>403</v>
+        <v>83</v>
       </c>
       <c r="D79" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="2" t="s">
-        <v>95</v>
-      </c>
+      <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="5" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="D80" s="3">
         <v>1</v>
@@ -6941,17 +7142,19 @@
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="5" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="D81" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="2"/>
+      <c r="A82" s="2" t="s">
+        <v>87</v>
+      </c>
       <c r="B82" s="2"/>
       <c r="C82" s="5" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D82" s="3">
         <v>1</v>
@@ -6961,7 +7164,7 @@
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="5" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="D83" s="3">
         <v>1</v>
@@ -6971,7 +7174,7 @@
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="5" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D84" s="3">
         <v>1</v>
@@ -6981,7 +7184,7 @@
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="5" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="D85" s="3">
         <v>1</v>
@@ -6991,7 +7194,7 @@
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="5" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D86" s="3">
         <v>1</v>
@@ -7001,7 +7204,7 @@
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="5" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D87" s="3">
         <v>1</v>
@@ -7011,7 +7214,7 @@
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="5" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D88" s="3">
         <v>1</v>
@@ -7021,17 +7224,17 @@
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="5" t="s">
-        <v>399</v>
+        <v>424</v>
       </c>
       <c r="D89" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="5" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="D90" s="3">
         <v>1</v>
@@ -7041,31 +7244,29 @@
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="5" t="s">
-        <v>433</v>
+        <v>403</v>
       </c>
       <c r="D91" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="2"/>
+      <c r="A92" s="2" t="s">
+        <v>95</v>
+      </c>
       <c r="B92" s="2"/>
       <c r="C92" s="5" t="s">
-        <v>404</v>
+        <v>96</v>
       </c>
       <c r="D92" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>412</v>
-      </c>
+      <c r="A93" s="2"/>
+      <c r="B93" s="2"/>
       <c r="C93" s="5" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D93" s="3">
         <v>1</v>
@@ -7075,7 +7276,7 @@
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="5" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D94" s="3">
         <v>1</v>
@@ -7085,7 +7286,7 @@
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="5" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D95" s="3">
         <v>1</v>
@@ -7095,7 +7296,7 @@
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="5" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="D96" s="3">
         <v>1</v>
@@ -7105,7 +7306,7 @@
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="5" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D97" s="3">
         <v>1</v>
@@ -7115,7 +7316,7 @@
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="5" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="D98" s="3">
         <v>1</v>
@@ -7125,7 +7326,7 @@
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="5" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="D99" s="3">
         <v>1</v>
@@ -7135,7 +7336,7 @@
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="5" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="D100" s="3">
         <v>1</v>
@@ -7145,17 +7346,17 @@
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="5" t="s">
-        <v>114</v>
+        <v>399</v>
       </c>
       <c r="D101" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="5" t="s">
-        <v>115</v>
+        <v>427</v>
       </c>
       <c r="D102" s="3">
         <v>1</v>
@@ -7165,7 +7366,7 @@
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="5" t="s">
-        <v>116</v>
+        <v>423</v>
       </c>
       <c r="D103" s="3">
         <v>1</v>
@@ -7175,29 +7376,31 @@
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="5" t="s">
-        <v>118</v>
+        <v>404</v>
       </c>
       <c r="D104" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="2"/>
-      <c r="B105" s="2"/>
+      <c r="A105" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>412</v>
+      </c>
       <c r="C105" s="5" t="s">
-        <v>406</v>
+        <v>106</v>
       </c>
       <c r="D105" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="2"/>
-      <c r="B106" s="2" t="s">
-        <v>117</v>
-      </c>
+      <c r="B106" s="2"/>
       <c r="C106" s="5" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="D106" s="3">
         <v>1</v>
@@ -7207,7 +7410,7 @@
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="5" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="D107" s="3">
         <v>1</v>
@@ -7217,7 +7420,7 @@
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="5" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="D108" s="3">
         <v>1</v>
@@ -7227,7 +7430,7 @@
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="5" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="D109" s="3">
         <v>1</v>
@@ -7237,7 +7440,7 @@
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="5" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="D110" s="3">
         <v>1</v>
@@ -7247,7 +7450,7 @@
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="5" t="s">
-        <v>400</v>
+        <v>112</v>
       </c>
       <c r="D111" s="3">
         <v>1</v>
@@ -7257,7 +7460,7 @@
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="5" t="s">
-        <v>401</v>
+        <v>113</v>
       </c>
       <c r="D112" s="3">
         <v>1</v>
@@ -7267,7 +7470,7 @@
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="5" t="s">
-        <v>417</v>
+        <v>114</v>
       </c>
       <c r="D113" s="3">
         <v>1</v>
@@ -7277,7 +7480,7 @@
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="5" t="s">
-        <v>418</v>
+        <v>115</v>
       </c>
       <c r="D114" s="3">
         <v>1</v>
@@ -7287,7 +7490,7 @@
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="5" t="s">
-        <v>438</v>
+        <v>116</v>
       </c>
       <c r="D115" s="3">
         <v>1</v>
@@ -7297,7 +7500,7 @@
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="5" t="s">
-        <v>439</v>
+        <v>118</v>
       </c>
       <c r="D116" s="3">
         <v>1</v>
@@ -7307,17 +7510,19 @@
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="5" t="s">
-        <v>440</v>
+        <v>406</v>
       </c>
       <c r="D117" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="2"/>
-      <c r="B118" s="2"/>
+      <c r="B118" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="C118" s="5" t="s">
-        <v>441</v>
+        <v>119</v>
       </c>
       <c r="D118" s="3">
         <v>1</v>
@@ -7327,7 +7532,7 @@
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="5" t="s">
-        <v>442</v>
+        <v>120</v>
       </c>
       <c r="D119" s="3">
         <v>1</v>
@@ -7337,7 +7542,7 @@
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="5" t="s">
-        <v>443</v>
+        <v>121</v>
       </c>
       <c r="D120" s="3">
         <v>1</v>
@@ -7347,7 +7552,7 @@
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="5" t="s">
-        <v>444</v>
+        <v>122</v>
       </c>
       <c r="D121" s="3">
         <v>1</v>
@@ -7357,7 +7562,7 @@
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="5" t="s">
-        <v>445</v>
+        <v>123</v>
       </c>
       <c r="D122" s="3">
         <v>1</v>
@@ -7365,11 +7570,9 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="2"/>
-      <c r="B123" s="2" t="s">
-        <v>124</v>
-      </c>
+      <c r="B123" s="2"/>
       <c r="C123" s="5" t="s">
-        <v>125</v>
+        <v>400</v>
       </c>
       <c r="D123" s="3">
         <v>1</v>
@@ -7379,7 +7582,7 @@
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="5" t="s">
-        <v>126</v>
+        <v>401</v>
       </c>
       <c r="D124" s="3">
         <v>1</v>
@@ -7389,7 +7592,7 @@
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="5" t="s">
-        <v>127</v>
+        <v>417</v>
       </c>
       <c r="D125" s="3">
         <v>1</v>
@@ -7399,19 +7602,17 @@
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="5" t="s">
-        <v>128</v>
+        <v>418</v>
       </c>
       <c r="D126" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A127" s="2" t="s">
-        <v>134</v>
-      </c>
+      <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="5" t="s">
-        <v>135</v>
+        <v>428</v>
       </c>
       <c r="D127" s="3">
         <v>1</v>
@@ -7421,7 +7622,7 @@
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="5" t="s">
-        <v>136</v>
+        <v>429</v>
       </c>
       <c r="D128" s="3">
         <v>1</v>
@@ -7431,7 +7632,7 @@
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="5" t="s">
-        <v>137</v>
+        <v>430</v>
       </c>
       <c r="D129" s="3">
         <v>1</v>
@@ -7441,7 +7642,7 @@
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="5" t="s">
-        <v>138</v>
+        <v>431</v>
       </c>
       <c r="D130" s="3">
         <v>1</v>
@@ -7451,7 +7652,7 @@
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="5" t="s">
-        <v>139</v>
+        <v>432</v>
       </c>
       <c r="D131" s="3">
         <v>1</v>
@@ -7461,7 +7662,7 @@
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="5" t="s">
-        <v>140</v>
+        <v>433</v>
       </c>
       <c r="D132" s="3">
         <v>1</v>
@@ -7471,19 +7672,17 @@
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="5" t="s">
-        <v>407</v>
+        <v>434</v>
       </c>
       <c r="D133" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A134" s="2" t="s">
-        <v>141</v>
-      </c>
+      <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="5" t="s">
-        <v>142</v>
+        <v>435</v>
       </c>
       <c r="D134" s="3">
         <v>1</v>
@@ -7491,9 +7690,11 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="2"/>
-      <c r="B135" s="2"/>
+      <c r="B135" s="2" t="s">
+        <v>124</v>
+      </c>
       <c r="C135" s="5" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="D135" s="3">
         <v>1</v>
@@ -7503,7 +7704,7 @@
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="5" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="D136" s="3">
         <v>1</v>
@@ -7513,7 +7714,7 @@
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="5" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="D137" s="3">
         <v>1</v>
@@ -7523,21 +7724,19 @@
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="5" t="s">
-        <v>408</v>
+        <v>128</v>
       </c>
       <c r="D138" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="B139" s="2" t="s">
-        <v>195</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="B139" s="2"/>
       <c r="C139" s="5" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="D139" s="3">
         <v>1</v>
@@ -7547,7 +7746,7 @@
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="5" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="D140" s="3">
         <v>1</v>
@@ -7557,7 +7756,7 @@
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="5" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="D141" s="3">
         <v>1</v>
@@ -7567,7 +7766,7 @@
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="5" t="s">
-        <v>211</v>
+        <v>138</v>
       </c>
       <c r="D142" s="3">
         <v>1</v>
@@ -7577,7 +7776,7 @@
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="5" t="s">
-        <v>213</v>
+        <v>139</v>
       </c>
       <c r="D143" s="3">
         <v>1</v>
@@ -7587,7 +7786,7 @@
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="5" t="s">
-        <v>212</v>
+        <v>140</v>
       </c>
       <c r="D144" s="3">
         <v>1</v>
@@ -7597,19 +7796,19 @@
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="5" t="s">
-        <v>214</v>
+        <v>407</v>
       </c>
       <c r="D145" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A146" s="2"/>
-      <c r="B146" s="2" t="s">
-        <v>196</v>
-      </c>
+      <c r="A146" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B146" s="2"/>
       <c r="C146" s="5" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="D146" s="3">
         <v>1</v>
@@ -7619,7 +7818,7 @@
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="5" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="D147" s="3">
         <v>1</v>
@@ -7629,7 +7828,7 @@
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="5" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="D148" s="3">
         <v>1</v>
@@ -7639,7 +7838,7 @@
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="5" t="s">
-        <v>215</v>
+        <v>145</v>
       </c>
       <c r="D149" s="3">
         <v>1</v>
@@ -7649,17 +7848,21 @@
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="5" t="s">
-        <v>216</v>
+        <v>408</v>
       </c>
       <c r="D150" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A151" s="2"/>
-      <c r="B151" s="2"/>
+      <c r="A151" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>195</v>
+      </c>
       <c r="C151" s="5" t="s">
-        <v>217</v>
+        <v>146</v>
       </c>
       <c r="D151" s="3">
         <v>1</v>
@@ -7669,7 +7872,7 @@
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="5" t="s">
-        <v>218</v>
+        <v>147</v>
       </c>
       <c r="D152" s="3">
         <v>1</v>
@@ -7677,11 +7880,9 @@
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" s="2"/>
-      <c r="B153" s="2" t="s">
-        <v>197</v>
-      </c>
+      <c r="B153" s="2"/>
       <c r="C153" s="5" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D153" s="3">
         <v>1</v>
@@ -7691,7 +7892,7 @@
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="5" t="s">
-        <v>153</v>
+        <v>211</v>
       </c>
       <c r="D154" s="3">
         <v>1</v>
@@ -7701,7 +7902,7 @@
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="5" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="D155" s="3">
         <v>1</v>
@@ -7711,7 +7912,7 @@
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="5" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="D156" s="3">
         <v>1</v>
@@ -7721,7 +7922,7 @@
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="5" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="D157" s="3">
         <v>1</v>
@@ -7729,9 +7930,11 @@
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" s="2"/>
-      <c r="B158" s="2"/>
+      <c r="B158" s="2" t="s">
+        <v>196</v>
+      </c>
       <c r="C158" s="5" t="s">
-        <v>221</v>
+        <v>149</v>
       </c>
       <c r="D158" s="3">
         <v>1</v>
@@ -7741,7 +7944,7 @@
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="5" t="s">
-        <v>222</v>
+        <v>150</v>
       </c>
       <c r="D159" s="3">
         <v>1</v>
@@ -7749,11 +7952,9 @@
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" s="2"/>
-      <c r="B160" s="2" t="s">
-        <v>198</v>
-      </c>
+      <c r="B160" s="2"/>
       <c r="C160" s="5" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D160" s="3">
         <v>1</v>
@@ -7763,7 +7964,7 @@
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="5" t="s">
-        <v>156</v>
+        <v>215</v>
       </c>
       <c r="D161" s="3">
         <v>1</v>
@@ -7773,7 +7974,7 @@
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="5" t="s">
-        <v>157</v>
+        <v>216</v>
       </c>
       <c r="D162" s="3">
         <v>1</v>
@@ -7783,7 +7984,7 @@
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="5" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D163" s="3">
         <v>1</v>
@@ -7793,7 +7994,7 @@
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D164" s="3">
         <v>1</v>
@@ -7801,9 +8002,11 @@
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" s="2"/>
-      <c r="B165" s="2"/>
+      <c r="B165" s="2" t="s">
+        <v>197</v>
+      </c>
       <c r="C165" s="5" t="s">
-        <v>225</v>
+        <v>152</v>
       </c>
       <c r="D165" s="3">
         <v>1</v>
@@ -7813,7 +8016,7 @@
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="5" t="s">
-        <v>226</v>
+        <v>153</v>
       </c>
       <c r="D166" s="3">
         <v>1</v>
@@ -7821,11 +8024,9 @@
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" s="2"/>
-      <c r="B167" s="2" t="s">
-        <v>199</v>
-      </c>
+      <c r="B167" s="2"/>
       <c r="C167" s="5" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D167" s="3">
         <v>1</v>
@@ -7835,7 +8036,7 @@
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="5" t="s">
-        <v>159</v>
+        <v>219</v>
       </c>
       <c r="D168" s="3">
         <v>1</v>
@@ -7845,7 +8046,7 @@
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="5" t="s">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="D169" s="3">
         <v>1</v>
@@ -7855,7 +8056,7 @@
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="5" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="D170" s="3">
         <v>1</v>
@@ -7865,7 +8066,7 @@
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="5" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="D171" s="3">
         <v>1</v>
@@ -7873,9 +8074,11 @@
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" s="2"/>
-      <c r="B172" s="2"/>
+      <c r="B172" s="2" t="s">
+        <v>198</v>
+      </c>
       <c r="C172" s="5" t="s">
-        <v>229</v>
+        <v>155</v>
       </c>
       <c r="D172" s="3">
         <v>1</v>
@@ -7885,7 +8088,7 @@
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="5" t="s">
-        <v>230</v>
+        <v>156</v>
       </c>
       <c r="D173" s="3">
         <v>1</v>
@@ -7893,11 +8096,9 @@
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" s="2"/>
-      <c r="B174" s="2" t="s">
-        <v>200</v>
-      </c>
+      <c r="B174" s="2"/>
       <c r="C174" s="5" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D174" s="3">
         <v>1</v>
@@ -7907,7 +8108,7 @@
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="5" t="s">
-        <v>162</v>
+        <v>223</v>
       </c>
       <c r="D175" s="3">
         <v>1</v>
@@ -7917,7 +8118,7 @@
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="5" t="s">
-        <v>163</v>
+        <v>224</v>
       </c>
       <c r="D176" s="3">
         <v>1</v>
@@ -7927,7 +8128,7 @@
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="5" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="D177" s="3">
         <v>1</v>
@@ -7937,7 +8138,7 @@
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="5" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="D178" s="3">
         <v>1</v>
@@ -7945,9 +8146,11 @@
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" s="2"/>
-      <c r="B179" s="2"/>
+      <c r="B179" s="2" t="s">
+        <v>199</v>
+      </c>
       <c r="C179" s="5" t="s">
-        <v>233</v>
+        <v>158</v>
       </c>
       <c r="D179" s="3">
         <v>1</v>
@@ -7957,7 +8160,7 @@
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="5" t="s">
-        <v>234</v>
+        <v>159</v>
       </c>
       <c r="D180" s="3">
         <v>1</v>
@@ -7965,11 +8168,9 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" s="2"/>
-      <c r="B181" s="2" t="s">
-        <v>201</v>
-      </c>
+      <c r="B181" s="2"/>
       <c r="C181" s="5" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D181" s="3">
         <v>1</v>
@@ -7979,7 +8180,7 @@
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="5" t="s">
-        <v>165</v>
+        <v>227</v>
       </c>
       <c r="D182" s="3">
         <v>1</v>
@@ -7989,7 +8190,7 @@
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="5" t="s">
-        <v>166</v>
+        <v>228</v>
       </c>
       <c r="D183" s="3">
         <v>1</v>
@@ -7999,7 +8200,7 @@
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="5" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="D184" s="3">
         <v>1</v>
@@ -8009,7 +8210,7 @@
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="5" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="D185" s="3">
         <v>1</v>
@@ -8017,9 +8218,11 @@
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" s="2"/>
-      <c r="B186" s="2"/>
+      <c r="B186" s="2" t="s">
+        <v>200</v>
+      </c>
       <c r="C186" s="5" t="s">
-        <v>237</v>
+        <v>161</v>
       </c>
       <c r="D186" s="3">
         <v>1</v>
@@ -8029,7 +8232,7 @@
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="5" t="s">
-        <v>238</v>
+        <v>162</v>
       </c>
       <c r="D187" s="3">
         <v>1</v>
@@ -8037,11 +8240,9 @@
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" s="2"/>
-      <c r="B188" s="2" t="s">
-        <v>202</v>
-      </c>
+      <c r="B188" s="2"/>
       <c r="C188" s="5" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D188" s="3">
         <v>1</v>
@@ -8051,7 +8252,7 @@
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="5" t="s">
-        <v>168</v>
+        <v>231</v>
       </c>
       <c r="D189" s="3">
         <v>1</v>
@@ -8061,7 +8262,7 @@
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="5" t="s">
-        <v>169</v>
+        <v>232</v>
       </c>
       <c r="D190" s="3">
         <v>1</v>
@@ -8071,7 +8272,7 @@
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="5" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="D191" s="3">
         <v>1</v>
@@ -8081,7 +8282,7 @@
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="5" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="D192" s="3">
         <v>1</v>
@@ -8089,9 +8290,11 @@
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" s="2"/>
-      <c r="B193" s="2"/>
+      <c r="B193" s="2" t="s">
+        <v>201</v>
+      </c>
       <c r="C193" s="5" t="s">
-        <v>241</v>
+        <v>164</v>
       </c>
       <c r="D193" s="3">
         <v>1</v>
@@ -8101,7 +8304,7 @@
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="5" t="s">
-        <v>242</v>
+        <v>165</v>
       </c>
       <c r="D194" s="3">
         <v>1</v>
@@ -8109,11 +8312,9 @@
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" s="2"/>
-      <c r="B195" s="2" t="s">
-        <v>203</v>
-      </c>
+      <c r="B195" s="2"/>
       <c r="C195" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D195" s="3">
         <v>1</v>
@@ -8123,7 +8324,7 @@
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="5" t="s">
-        <v>171</v>
+        <v>235</v>
       </c>
       <c r="D196" s="3">
         <v>1</v>
@@ -8133,7 +8334,7 @@
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="5" t="s">
-        <v>172</v>
+        <v>236</v>
       </c>
       <c r="D197" s="3">
         <v>1</v>
@@ -8143,7 +8344,7 @@
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="5" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D198" s="3">
         <v>1</v>
@@ -8153,7 +8354,7 @@
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="5" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="D199" s="3">
         <v>1</v>
@@ -8161,9 +8362,11 @@
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" s="2"/>
-      <c r="B200" s="2"/>
+      <c r="B200" s="2" t="s">
+        <v>202</v>
+      </c>
       <c r="C200" s="5" t="s">
-        <v>245</v>
+        <v>167</v>
       </c>
       <c r="D200" s="3">
         <v>1</v>
@@ -8173,7 +8376,7 @@
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="5" t="s">
-        <v>246</v>
+        <v>168</v>
       </c>
       <c r="D201" s="3">
         <v>1</v>
@@ -8181,11 +8384,9 @@
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" s="2"/>
-      <c r="B202" s="2" t="s">
-        <v>204</v>
-      </c>
+      <c r="B202" s="2"/>
       <c r="C202" s="5" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D202" s="3">
         <v>1</v>
@@ -8195,7 +8396,7 @@
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="5" t="s">
-        <v>174</v>
+        <v>239</v>
       </c>
       <c r="D203" s="3">
         <v>1</v>
@@ -8205,7 +8406,7 @@
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="5" t="s">
-        <v>175</v>
+        <v>240</v>
       </c>
       <c r="D204" s="3">
         <v>1</v>
@@ -8215,7 +8416,7 @@
       <c r="A205" s="2"/>
       <c r="B205" s="2"/>
       <c r="C205" s="5" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D205" s="3">
         <v>1</v>
@@ -8225,7 +8426,7 @@
       <c r="A206" s="2"/>
       <c r="B206" s="2"/>
       <c r="C206" s="5" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="D206" s="3">
         <v>1</v>
@@ -8233,9 +8434,11 @@
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" s="2"/>
-      <c r="B207" s="2"/>
+      <c r="B207" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="C207" s="5" t="s">
-        <v>249</v>
+        <v>170</v>
       </c>
       <c r="D207" s="3">
         <v>1</v>
@@ -8245,7 +8448,7 @@
       <c r="A208" s="2"/>
       <c r="B208" s="2"/>
       <c r="C208" s="5" t="s">
-        <v>250</v>
+        <v>171</v>
       </c>
       <c r="D208" s="3">
         <v>1</v>
@@ -8253,11 +8456,9 @@
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" s="2"/>
-      <c r="B209" s="2" t="s">
-        <v>205</v>
-      </c>
+      <c r="B209" s="2"/>
       <c r="C209" s="5" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D209" s="3">
         <v>1</v>
@@ -8267,7 +8468,7 @@
       <c r="A210" s="2"/>
       <c r="B210" s="2"/>
       <c r="C210" s="5" t="s">
-        <v>177</v>
+        <v>243</v>
       </c>
       <c r="D210" s="3">
         <v>1</v>
@@ -8277,7 +8478,7 @@
       <c r="A211" s="2"/>
       <c r="B211" s="2"/>
       <c r="C211" s="5" t="s">
-        <v>178</v>
+        <v>244</v>
       </c>
       <c r="D211" s="3">
         <v>1</v>
@@ -8287,7 +8488,7 @@
       <c r="A212" s="2"/>
       <c r="B212" s="2"/>
       <c r="C212" s="5" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="D212" s="3">
         <v>1</v>
@@ -8297,7 +8498,7 @@
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="5" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="D213" s="3">
         <v>1</v>
@@ -8305,9 +8506,11 @@
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" s="2"/>
-      <c r="B214" s="2"/>
+      <c r="B214" s="2" t="s">
+        <v>204</v>
+      </c>
       <c r="C214" s="5" t="s">
-        <v>253</v>
+        <v>173</v>
       </c>
       <c r="D214" s="3">
         <v>1</v>
@@ -8317,7 +8520,7 @@
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="5" t="s">
-        <v>254</v>
+        <v>174</v>
       </c>
       <c r="D215" s="3">
         <v>1</v>
@@ -8325,11 +8528,9 @@
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" s="2"/>
-      <c r="B216" s="2" t="s">
-        <v>206</v>
-      </c>
+      <c r="B216" s="2"/>
       <c r="C216" s="5" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D216" s="3">
         <v>1</v>
@@ -8339,7 +8540,7 @@
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="5" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="D217" s="3">
         <v>1</v>
@@ -8349,7 +8550,7 @@
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="5" t="s">
-        <v>181</v>
+        <v>248</v>
       </c>
       <c r="D218" s="3">
         <v>1</v>
@@ -8359,7 +8560,7 @@
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="5" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="D219" s="3">
         <v>1</v>
@@ -8369,7 +8570,7 @@
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="5" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="D220" s="3">
         <v>1</v>
@@ -8377,9 +8578,11 @@
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" s="2"/>
-      <c r="B221" s="2"/>
+      <c r="B221" s="2" t="s">
+        <v>205</v>
+      </c>
       <c r="C221" s="5" t="s">
-        <v>257</v>
+        <v>176</v>
       </c>
       <c r="D221" s="3">
         <v>1</v>
@@ -8389,7 +8592,7 @@
       <c r="A222" s="2"/>
       <c r="B222" s="2"/>
       <c r="C222" s="5" t="s">
-        <v>258</v>
+        <v>177</v>
       </c>
       <c r="D222" s="3">
         <v>1</v>
@@ -8397,11 +8600,9 @@
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" s="2"/>
-      <c r="B223" s="2" t="s">
-        <v>207</v>
-      </c>
+      <c r="B223" s="2"/>
       <c r="C223" s="5" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D223" s="3">
         <v>1</v>
@@ -8411,7 +8612,7 @@
       <c r="A224" s="2"/>
       <c r="B224" s="2"/>
       <c r="C224" s="5" t="s">
-        <v>183</v>
+        <v>251</v>
       </c>
       <c r="D224" s="3">
         <v>1</v>
@@ -8421,7 +8622,7 @@
       <c r="A225" s="2"/>
       <c r="B225" s="2"/>
       <c r="C225" s="5" t="s">
-        <v>184</v>
+        <v>252</v>
       </c>
       <c r="D225" s="3">
         <v>1</v>
@@ -8431,7 +8632,7 @@
       <c r="A226" s="2"/>
       <c r="B226" s="2"/>
       <c r="C226" s="5" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="D226" s="3">
         <v>1</v>
@@ -8441,7 +8642,7 @@
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="5" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="D227" s="3">
         <v>1</v>
@@ -8449,9 +8650,11 @@
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" s="2"/>
-      <c r="B228" s="2"/>
+      <c r="B228" s="2" t="s">
+        <v>206</v>
+      </c>
       <c r="C228" s="5" t="s">
-        <v>261</v>
+        <v>179</v>
       </c>
       <c r="D228" s="3">
         <v>1</v>
@@ -8461,7 +8664,7 @@
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
       <c r="C229" s="5" t="s">
-        <v>262</v>
+        <v>180</v>
       </c>
       <c r="D229" s="3">
         <v>1</v>
@@ -8469,11 +8672,9 @@
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" s="2"/>
-      <c r="B230" s="2" t="s">
-        <v>208</v>
-      </c>
+      <c r="B230" s="2"/>
       <c r="C230" s="5" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D230" s="3">
         <v>1</v>
@@ -8483,7 +8684,7 @@
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
       <c r="C231" s="5" t="s">
-        <v>186</v>
+        <v>255</v>
       </c>
       <c r="D231" s="3">
         <v>1</v>
@@ -8493,7 +8694,7 @@
       <c r="A232" s="2"/>
       <c r="B232" s="2"/>
       <c r="C232" s="5" t="s">
-        <v>187</v>
+        <v>256</v>
       </c>
       <c r="D232" s="3">
         <v>1</v>
@@ -8503,7 +8704,7 @@
       <c r="A233" s="2"/>
       <c r="B233" s="2"/>
       <c r="C233" s="5" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="D233" s="3">
         <v>1</v>
@@ -8513,7 +8714,7 @@
       <c r="A234" s="2"/>
       <c r="B234" s="2"/>
       <c r="C234" s="5" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="D234" s="3">
         <v>1</v>
@@ -8521,9 +8722,11 @@
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" s="2"/>
-      <c r="B235" s="2"/>
+      <c r="B235" s="2" t="s">
+        <v>207</v>
+      </c>
       <c r="C235" s="5" t="s">
-        <v>265</v>
+        <v>182</v>
       </c>
       <c r="D235" s="3">
         <v>1</v>
@@ -8533,7 +8736,7 @@
       <c r="A236" s="2"/>
       <c r="B236" s="2"/>
       <c r="C236" s="5" t="s">
-        <v>266</v>
+        <v>183</v>
       </c>
       <c r="D236" s="3">
         <v>1</v>
@@ -8541,11 +8744,9 @@
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" s="2"/>
-      <c r="B237" s="2" t="s">
-        <v>209</v>
-      </c>
+      <c r="B237" s="2"/>
       <c r="C237" s="5" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D237" s="3">
         <v>1</v>
@@ -8555,7 +8756,7 @@
       <c r="A238" s="2"/>
       <c r="B238" s="2"/>
       <c r="C238" s="5" t="s">
-        <v>189</v>
+        <v>259</v>
       </c>
       <c r="D238" s="3">
         <v>1</v>
@@ -8565,7 +8766,7 @@
       <c r="A239" s="2"/>
       <c r="B239" s="2"/>
       <c r="C239" s="5" t="s">
-        <v>190</v>
+        <v>260</v>
       </c>
       <c r="D239" s="3">
         <v>1</v>
@@ -8575,7 +8776,7 @@
       <c r="A240" s="2"/>
       <c r="B240" s="2"/>
       <c r="C240" s="5" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D240" s="3">
         <v>1</v>
@@ -8585,7 +8786,7 @@
       <c r="A241" s="2"/>
       <c r="B241" s="2"/>
       <c r="C241" s="5" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="D241" s="3">
         <v>1</v>
@@ -8593,9 +8794,11 @@
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" s="2"/>
-      <c r="B242" s="2"/>
+      <c r="B242" s="2" t="s">
+        <v>208</v>
+      </c>
       <c r="C242" s="5" t="s">
-        <v>269</v>
+        <v>185</v>
       </c>
       <c r="D242" s="3">
         <v>1</v>
@@ -8605,7 +8808,7 @@
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="5" t="s">
-        <v>270</v>
+        <v>186</v>
       </c>
       <c r="D243" s="3">
         <v>1</v>
@@ -8613,11 +8816,9 @@
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" s="2"/>
-      <c r="B244" s="2" t="s">
-        <v>210</v>
-      </c>
+      <c r="B244" s="2"/>
       <c r="C244" s="5" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D244" s="3">
         <v>1</v>
@@ -8627,7 +8828,7 @@
       <c r="A245" s="2"/>
       <c r="B245" s="2"/>
       <c r="C245" s="5" t="s">
-        <v>192</v>
+        <v>263</v>
       </c>
       <c r="D245" s="3">
         <v>1</v>
@@ -8637,7 +8838,7 @@
       <c r="A246" s="2"/>
       <c r="B246" s="2"/>
       <c r="C246" s="5" t="s">
-        <v>193</v>
+        <v>264</v>
       </c>
       <c r="D246" s="3">
         <v>1</v>
@@ -8646,8 +8847,8 @@
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" s="2"/>
       <c r="B247" s="2"/>
-      <c r="C247" s="7" t="s">
-        <v>271</v>
+      <c r="C247" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="D247" s="3">
         <v>1</v>
@@ -8656,8 +8857,8 @@
     <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" s="2"/>
       <c r="B248" s="2"/>
-      <c r="C248" s="7" t="s">
-        <v>272</v>
+      <c r="C248" s="5" t="s">
+        <v>266</v>
       </c>
       <c r="D248" s="3">
         <v>1</v>
@@ -8665,9 +8866,11 @@
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" s="2"/>
-      <c r="B249" s="2"/>
-      <c r="C249" s="7" t="s">
-        <v>273</v>
+      <c r="B249" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C249" s="5" t="s">
+        <v>188</v>
       </c>
       <c r="D249" s="3">
         <v>1</v>
@@ -8676,22 +8879,18 @@
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" s="2"/>
       <c r="B250" s="2"/>
-      <c r="C250" s="7" t="s">
-        <v>274</v>
+      <c r="C250" s="5" t="s">
+        <v>189</v>
       </c>
       <c r="D250" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A251" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="B251" s="2" t="s">
-        <v>413</v>
-      </c>
+      <c r="A251" s="2"/>
+      <c r="B251" s="2"/>
       <c r="C251" s="5" t="s">
-        <v>276</v>
+        <v>190</v>
       </c>
       <c r="D251" s="3">
         <v>1</v>
@@ -8701,7 +8900,7 @@
       <c r="A252" s="2"/>
       <c r="B252" s="2"/>
       <c r="C252" s="5" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="D252" s="3">
         <v>1</v>
@@ -8711,7 +8910,7 @@
       <c r="A253" s="2"/>
       <c r="B253" s="2"/>
       <c r="C253" s="5" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="D253" s="3">
         <v>1</v>
@@ -8721,7 +8920,7 @@
       <c r="A254" s="2"/>
       <c r="B254" s="2"/>
       <c r="C254" s="5" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="D254" s="3">
         <v>1</v>
@@ -8731,7 +8930,7 @@
       <c r="A255" s="2"/>
       <c r="B255" s="2"/>
       <c r="C255" s="5" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="D255" s="3">
         <v>1</v>
@@ -8739,9 +8938,11 @@
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" s="2"/>
-      <c r="B256" s="2"/>
+      <c r="B256" s="2" t="s">
+        <v>210</v>
+      </c>
       <c r="C256" s="5" t="s">
-        <v>281</v>
+        <v>191</v>
       </c>
       <c r="D256" s="3">
         <v>1</v>
@@ -8751,7 +8952,7 @@
       <c r="A257" s="2"/>
       <c r="B257" s="2"/>
       <c r="C257" s="5" t="s">
-        <v>282</v>
+        <v>192</v>
       </c>
       <c r="D257" s="3">
         <v>1</v>
@@ -8761,7 +8962,7 @@
       <c r="A258" s="2"/>
       <c r="B258" s="2"/>
       <c r="C258" s="5" t="s">
-        <v>446</v>
+        <v>193</v>
       </c>
       <c r="D258" s="3">
         <v>1</v>
@@ -8770,8 +8971,8 @@
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" s="2"/>
       <c r="B259" s="2"/>
-      <c r="C259" s="5" t="s">
-        <v>447</v>
+      <c r="C259" s="7" t="s">
+        <v>271</v>
       </c>
       <c r="D259" s="3">
         <v>1</v>
@@ -8780,8 +8981,8 @@
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" s="2"/>
       <c r="B260" s="2"/>
-      <c r="C260" s="5" t="s">
-        <v>283</v>
+      <c r="C260" s="7" t="s">
+        <v>272</v>
       </c>
       <c r="D260" s="3">
         <v>1</v>
@@ -8790,8 +8991,8 @@
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" s="2"/>
       <c r="B261" s="2"/>
-      <c r="C261" s="5" t="s">
-        <v>284</v>
+      <c r="C261" s="7" t="s">
+        <v>273</v>
       </c>
       <c r="D261" s="3">
         <v>1</v>
@@ -8800,20 +9001,22 @@
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" s="2"/>
       <c r="B262" s="2"/>
-      <c r="C262" s="5" t="s">
-        <v>409</v>
+      <c r="C262" s="7" t="s">
+        <v>274</v>
       </c>
       <c r="D262" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A263" s="2"/>
+      <c r="A263" s="2" t="s">
+        <v>275</v>
+      </c>
       <c r="B263" s="2" t="s">
-        <v>117</v>
+        <v>413</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="D263" s="3">
         <v>1</v>
@@ -8823,7 +9026,7 @@
       <c r="A264" s="2"/>
       <c r="B264" s="2"/>
       <c r="C264" s="5" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="D264" s="3">
         <v>1</v>
@@ -8833,7 +9036,7 @@
       <c r="A265" s="2"/>
       <c r="B265" s="2"/>
       <c r="C265" s="5" t="s">
-        <v>346</v>
+        <v>278</v>
       </c>
       <c r="D265" s="3">
         <v>1</v>
@@ -8843,7 +9046,7 @@
       <c r="A266" s="2"/>
       <c r="B266" s="2"/>
       <c r="C266" s="5" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="D266" s="3">
         <v>1</v>
@@ -8853,21 +9056,17 @@
       <c r="A267" s="2"/>
       <c r="B267" s="2"/>
       <c r="C267" s="5" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="D267" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A268" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="B268" s="2" t="s">
-        <v>290</v>
-      </c>
+      <c r="A268" s="2"/>
+      <c r="B268" s="2"/>
       <c r="C268" s="5" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="D268" s="3">
         <v>1</v>
@@ -8877,7 +9076,7 @@
       <c r="A269" s="2"/>
       <c r="B269" s="2"/>
       <c r="C269" s="5" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="D269" s="3">
         <v>1</v>
@@ -8887,7 +9086,7 @@
       <c r="A270" s="2"/>
       <c r="B270" s="2"/>
       <c r="C270" s="5" t="s">
-        <v>293</v>
+        <v>436</v>
       </c>
       <c r="D270" s="3">
         <v>1</v>
@@ -8897,7 +9096,7 @@
       <c r="A271" s="2"/>
       <c r="B271" s="2"/>
       <c r="C271" s="5" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="D271" s="3">
         <v>1</v>
@@ -8907,7 +9106,7 @@
       <c r="A272" s="2"/>
       <c r="B272" s="2"/>
       <c r="C272" s="5" t="s">
-        <v>431</v>
+        <v>283</v>
       </c>
       <c r="D272" s="3">
         <v>1</v>
@@ -8915,11 +9114,9 @@
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" s="2"/>
-      <c r="B273" s="2" t="s">
-        <v>306</v>
-      </c>
+      <c r="B273" s="2"/>
       <c r="C273" s="5" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="D273" s="3">
         <v>1</v>
@@ -8929,17 +9126,19 @@
       <c r="A274" s="2"/>
       <c r="B274" s="2"/>
       <c r="C274" s="5" t="s">
-        <v>295</v>
+        <v>409</v>
       </c>
       <c r="D274" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" s="2"/>
-      <c r="B275" s="2"/>
+      <c r="B275" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="C275" s="5" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="D275" s="3">
         <v>1</v>
@@ -8949,7 +9148,7 @@
       <c r="A276" s="2"/>
       <c r="B276" s="2"/>
       <c r="C276" s="5" t="s">
-        <v>423</v>
+        <v>286</v>
       </c>
       <c r="D276" s="3">
         <v>1</v>
@@ -8959,7 +9158,7 @@
       <c r="A277" s="2"/>
       <c r="B277" s="2"/>
       <c r="C277" s="5" t="s">
-        <v>424</v>
+        <v>462</v>
       </c>
       <c r="D277" s="3">
         <v>1</v>
@@ -8967,11 +9166,9 @@
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" s="2"/>
-      <c r="B278" s="2" t="s">
-        <v>307</v>
-      </c>
+      <c r="B278" s="2"/>
       <c r="C278" s="5" t="s">
-        <v>297</v>
+        <v>463</v>
       </c>
       <c r="D278" s="3">
         <v>1</v>
@@ -8981,7 +9178,7 @@
       <c r="A279" s="2"/>
       <c r="B279" s="2"/>
       <c r="C279" s="5" t="s">
-        <v>298</v>
+        <v>346</v>
       </c>
       <c r="D279" s="3">
         <v>1</v>
@@ -8991,7 +9188,7 @@
       <c r="A280" s="2"/>
       <c r="B280" s="2"/>
       <c r="C280" s="5" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="D280" s="3">
         <v>1</v>
@@ -9001,17 +9198,21 @@
       <c r="A281" s="2"/>
       <c r="B281" s="2"/>
       <c r="C281" s="5" t="s">
-        <v>430</v>
+        <v>288</v>
       </c>
       <c r="D281" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A282" s="2"/>
-      <c r="B282" s="2"/>
+      <c r="A282" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="B282" s="2" t="s">
+        <v>290</v>
+      </c>
       <c r="C282" s="5" t="s">
-        <v>429</v>
+        <v>291</v>
       </c>
       <c r="D282" s="3">
         <v>1</v>
@@ -9019,11 +9220,9 @@
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" s="2"/>
-      <c r="B283" s="2" t="s">
-        <v>308</v>
-      </c>
+      <c r="B283" s="2"/>
       <c r="C283" s="5" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="D283" s="3">
         <v>1</v>
@@ -9033,7 +9232,7 @@
       <c r="A284" s="2"/>
       <c r="B284" s="2"/>
       <c r="C284" s="5" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="D284" s="3">
         <v>1</v>
@@ -9043,7 +9242,7 @@
       <c r="A285" s="2"/>
       <c r="B285" s="2"/>
       <c r="C285" s="5" t="s">
-        <v>302</v>
+        <v>450</v>
       </c>
       <c r="D285" s="3">
         <v>1</v>
@@ -9053,7 +9252,7 @@
       <c r="A286" s="2"/>
       <c r="B286" s="2"/>
       <c r="C286" s="5" t="s">
-        <v>428</v>
+        <v>451</v>
       </c>
       <c r="D286" s="3">
         <v>1</v>
@@ -9061,9 +9260,11 @@
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" s="2"/>
-      <c r="B287" s="2"/>
+      <c r="B287" s="2" t="s">
+        <v>306</v>
+      </c>
       <c r="C287" s="5" t="s">
-        <v>427</v>
+        <v>294</v>
       </c>
       <c r="D287" s="3">
         <v>1</v>
@@ -9071,11 +9272,9 @@
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" s="2"/>
-      <c r="B288" s="2" t="s">
-        <v>309</v>
-      </c>
+      <c r="B288" s="2"/>
       <c r="C288" s="5" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D288" s="3">
         <v>1</v>
@@ -9085,7 +9284,7 @@
       <c r="A289" s="2"/>
       <c r="B289" s="2"/>
       <c r="C289" s="5" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="D289" s="3">
         <v>1</v>
@@ -9095,7 +9294,7 @@
       <c r="A290" s="2"/>
       <c r="B290" s="2"/>
       <c r="C290" s="5" t="s">
-        <v>305</v>
+        <v>452</v>
       </c>
       <c r="D290" s="3">
         <v>1</v>
@@ -9105,7 +9304,7 @@
       <c r="A291" s="2"/>
       <c r="B291" s="2"/>
       <c r="C291" s="5" t="s">
-        <v>425</v>
+        <v>453</v>
       </c>
       <c r="D291" s="3">
         <v>1</v>
@@ -9113,9 +9312,11 @@
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" s="2"/>
-      <c r="B292" s="2"/>
+      <c r="B292" s="2" t="s">
+        <v>307</v>
+      </c>
       <c r="C292" s="5" t="s">
-        <v>426</v>
+        <v>297</v>
       </c>
       <c r="D292" s="3">
         <v>1</v>
@@ -9123,11 +9324,9 @@
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" s="2"/>
-      <c r="B293" s="2" t="s">
-        <v>312</v>
-      </c>
+      <c r="B293" s="2"/>
       <c r="C293" s="5" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="D293" s="3">
         <v>1</v>
@@ -9137,19 +9336,17 @@
       <c r="A294" s="2"/>
       <c r="B294" s="2"/>
       <c r="C294" s="5" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="D294" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A295" s="2" t="s">
-        <v>313</v>
-      </c>
+      <c r="A295" s="2"/>
       <c r="B295" s="2"/>
       <c r="C295" s="5" t="s">
-        <v>314</v>
+        <v>454</v>
       </c>
       <c r="D295" s="3">
         <v>1</v>
@@ -9159,7 +9356,7 @@
       <c r="A296" s="2"/>
       <c r="B296" s="2"/>
       <c r="C296" s="5" t="s">
-        <v>315</v>
+        <v>455</v>
       </c>
       <c r="D296" s="3">
         <v>1</v>
@@ -9167,33 +9364,31 @@
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" s="2"/>
-      <c r="B297" s="2"/>
-      <c r="C297" s="7" t="s">
-        <v>316</v>
+      <c r="B297" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C297" s="5" t="s">
+        <v>300</v>
       </c>
       <c r="D297" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" s="2"/>
       <c r="B298" s="2"/>
       <c r="C298" s="5" t="s">
-        <v>402</v>
+        <v>301</v>
       </c>
       <c r="D298" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A299" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="B299" s="2" t="s">
-        <v>414</v>
-      </c>
+      <c r="A299" s="2"/>
+      <c r="B299" s="2"/>
       <c r="C299" s="5" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="D299" s="3">
         <v>1</v>
@@ -9203,7 +9398,7 @@
       <c r="A300" s="2"/>
       <c r="B300" s="2"/>
       <c r="C300" s="5" t="s">
-        <v>318</v>
+        <v>456</v>
       </c>
       <c r="D300" s="3">
         <v>1</v>
@@ -9213,7 +9408,7 @@
       <c r="A301" s="2"/>
       <c r="B301" s="2"/>
       <c r="C301" s="5" t="s">
-        <v>319</v>
+        <v>457</v>
       </c>
       <c r="D301" s="3">
         <v>1</v>
@@ -9221,9 +9416,11 @@
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" s="2"/>
-      <c r="B302" s="2"/>
+      <c r="B302" s="2" t="s">
+        <v>309</v>
+      </c>
       <c r="C302" s="5" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="D302" s="3">
         <v>1</v>
@@ -9233,7 +9430,7 @@
       <c r="A303" s="2"/>
       <c r="B303" s="2"/>
       <c r="C303" s="5" t="s">
-        <v>321</v>
+        <v>304</v>
       </c>
       <c r="D303" s="3">
         <v>1</v>
@@ -9243,7 +9440,7 @@
       <c r="A304" s="2"/>
       <c r="B304" s="2"/>
       <c r="C304" s="5" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="D304" s="3">
         <v>1</v>
@@ -9253,7 +9450,7 @@
       <c r="A305" s="2"/>
       <c r="B305" s="2"/>
       <c r="C305" s="5" t="s">
-        <v>323</v>
+        <v>458</v>
       </c>
       <c r="D305" s="3">
         <v>1</v>
@@ -9263,7 +9460,7 @@
       <c r="A306" s="2"/>
       <c r="B306" s="2"/>
       <c r="C306" s="5" t="s">
-        <v>324</v>
+        <v>459</v>
       </c>
       <c r="D306" s="3">
         <v>1</v>
@@ -9271,9 +9468,11 @@
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" s="2"/>
-      <c r="B307" s="2"/>
+      <c r="B307" s="2" t="s">
+        <v>312</v>
+      </c>
       <c r="C307" s="5" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="D307" s="3">
         <v>1</v>
@@ -9281,11 +9480,9 @@
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" s="2"/>
-      <c r="B308" s="2" t="s">
-        <v>364</v>
-      </c>
+      <c r="B308" s="2"/>
       <c r="C308" s="5" t="s">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="D308" s="3">
         <v>1</v>
@@ -9293,19 +9490,23 @@
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" s="2"/>
-      <c r="B309" s="2"/>
+      <c r="B309" s="2" t="s">
+        <v>460</v>
+      </c>
       <c r="C309" s="5" t="s">
-        <v>327</v>
+        <v>461</v>
       </c>
       <c r="D309" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A310" s="2"/>
+      <c r="A310" s="2" t="s">
+        <v>313</v>
+      </c>
       <c r="B310" s="2"/>
       <c r="C310" s="5" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="D310" s="3">
         <v>1</v>
@@ -9315,7 +9516,7 @@
       <c r="A311" s="2"/>
       <c r="B311" s="2"/>
       <c r="C311" s="5" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="D311" s="3">
         <v>1</v>
@@ -9324,28 +9525,32 @@
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" s="2"/>
       <c r="B312" s="2"/>
-      <c r="C312" s="5" t="s">
-        <v>330</v>
+      <c r="C312" s="7" t="s">
+        <v>316</v>
       </c>
       <c r="D312" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" s="2"/>
       <c r="B313" s="2"/>
       <c r="C313" s="5" t="s">
-        <v>331</v>
+        <v>402</v>
       </c>
       <c r="D313" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A314" s="2"/>
-      <c r="B314" s="2"/>
+      <c r="A314" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B314" s="2" t="s">
+        <v>414</v>
+      </c>
       <c r="C314" s="5" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="D314" s="3">
         <v>1</v>
@@ -9355,7 +9560,7 @@
       <c r="A315" s="2"/>
       <c r="B315" s="2"/>
       <c r="C315" s="5" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="D315" s="3">
         <v>1</v>
@@ -9365,7 +9570,7 @@
       <c r="A316" s="2"/>
       <c r="B316" s="2"/>
       <c r="C316" s="5" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="D316" s="3">
         <v>1</v>
@@ -9375,7 +9580,7 @@
       <c r="A317" s="2"/>
       <c r="B317" s="2"/>
       <c r="C317" s="5" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="D317" s="3">
         <v>1</v>
@@ -9385,7 +9590,7 @@
       <c r="A318" s="2"/>
       <c r="B318" s="2"/>
       <c r="C318" s="5" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="D318" s="3">
         <v>1</v>
@@ -9395,7 +9600,7 @@
       <c r="A319" s="2"/>
       <c r="B319" s="2"/>
       <c r="C319" s="5" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="D319" s="3">
         <v>1</v>
@@ -9405,7 +9610,7 @@
       <c r="A320" s="2"/>
       <c r="B320" s="2"/>
       <c r="C320" s="5" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="D320" s="3">
         <v>1</v>
@@ -9415,7 +9620,7 @@
       <c r="A321" s="2"/>
       <c r="B321" s="2"/>
       <c r="C321" s="5" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="D321" s="3">
         <v>1</v>
@@ -9425,7 +9630,7 @@
       <c r="A322" s="2"/>
       <c r="B322" s="2"/>
       <c r="C322" s="5" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="D322" s="3">
         <v>1</v>
@@ -9433,9 +9638,11 @@
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" s="2"/>
-      <c r="B323" s="2"/>
+      <c r="B323" s="2" t="s">
+        <v>364</v>
+      </c>
       <c r="C323" s="5" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="D323" s="3">
         <v>1</v>
@@ -9445,7 +9652,7 @@
       <c r="A324" s="2"/>
       <c r="B324" s="2"/>
       <c r="C324" s="5" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="D324" s="3">
         <v>1</v>
@@ -9455,7 +9662,7 @@
       <c r="A325" s="2"/>
       <c r="B325" s="2"/>
       <c r="C325" s="5" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="D325" s="3">
         <v>1</v>
@@ -9465,7 +9672,7 @@
       <c r="A326" s="2"/>
       <c r="B326" s="2"/>
       <c r="C326" s="5" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="D326" s="3">
         <v>1</v>
@@ -9475,7 +9682,7 @@
       <c r="A327" s="2"/>
       <c r="B327" s="2"/>
       <c r="C327" s="5" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="D327" s="3">
         <v>1</v>
@@ -9485,7 +9692,7 @@
       <c r="A328" s="2"/>
       <c r="B328" s="2"/>
       <c r="C328" s="5" t="s">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="D328" s="3">
         <v>1</v>
@@ -9495,7 +9702,7 @@
       <c r="A329" s="2"/>
       <c r="B329" s="2"/>
       <c r="C329" s="5" t="s">
-        <v>361</v>
+        <v>332</v>
       </c>
       <c r="D329" s="3">
         <v>1</v>
@@ -9505,7 +9712,7 @@
       <c r="A330" s="2"/>
       <c r="B330" s="2"/>
       <c r="C330" s="5" t="s">
-        <v>362</v>
+        <v>333</v>
       </c>
       <c r="D330" s="3">
         <v>1</v>
@@ -9515,7 +9722,7 @@
       <c r="A331" s="2"/>
       <c r="B331" s="2"/>
       <c r="C331" s="5" t="s">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="D331" s="3">
         <v>1</v>
@@ -9525,7 +9732,7 @@
       <c r="A332" s="2"/>
       <c r="B332" s="2"/>
       <c r="C332" s="5" t="s">
-        <v>388</v>
+        <v>335</v>
       </c>
       <c r="D332" s="3">
         <v>1</v>
@@ -9535,7 +9742,7 @@
       <c r="A333" s="2"/>
       <c r="B333" s="2"/>
       <c r="C333" s="5" t="s">
-        <v>389</v>
+        <v>336</v>
       </c>
       <c r="D333" s="3">
         <v>1</v>
@@ -9545,7 +9752,7 @@
       <c r="A334" s="2"/>
       <c r="B334" s="2"/>
       <c r="C334" s="5" t="s">
-        <v>390</v>
+        <v>337</v>
       </c>
       <c r="D334" s="3">
         <v>1</v>
@@ -9555,7 +9762,7 @@
       <c r="A335" s="2"/>
       <c r="B335" s="2"/>
       <c r="C335" s="5" t="s">
-        <v>391</v>
+        <v>338</v>
       </c>
       <c r="D335" s="3">
         <v>1</v>
@@ -9565,7 +9772,7 @@
       <c r="A336" s="2"/>
       <c r="B336" s="2"/>
       <c r="C336" s="5" t="s">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="D336" s="3">
         <v>1</v>
@@ -9575,7 +9782,7 @@
       <c r="A337" s="2"/>
       <c r="B337" s="2"/>
       <c r="C337" s="5" t="s">
-        <v>357</v>
+        <v>340</v>
       </c>
       <c r="D337" s="3">
         <v>1</v>
@@ -9585,7 +9792,7 @@
       <c r="A338" s="2"/>
       <c r="B338" s="2"/>
       <c r="C338" s="5" t="s">
-        <v>366</v>
+        <v>341</v>
       </c>
       <c r="D338" s="3">
         <v>1</v>
@@ -9595,7 +9802,7 @@
       <c r="A339" s="2"/>
       <c r="B339" s="2"/>
       <c r="C339" s="5" t="s">
-        <v>367</v>
+        <v>342</v>
       </c>
       <c r="D339" s="3">
         <v>1</v>
@@ -9605,7 +9812,7 @@
       <c r="A340" s="2"/>
       <c r="B340" s="2"/>
       <c r="C340" s="5" t="s">
-        <v>368</v>
+        <v>343</v>
       </c>
       <c r="D340" s="3">
         <v>1</v>
@@ -9615,7 +9822,7 @@
       <c r="A341" s="2"/>
       <c r="B341" s="2"/>
       <c r="C341" s="5" t="s">
-        <v>369</v>
+        <v>344</v>
       </c>
       <c r="D341" s="3">
         <v>1</v>
@@ -9625,7 +9832,7 @@
       <c r="A342" s="2"/>
       <c r="B342" s="2"/>
       <c r="C342" s="5" t="s">
-        <v>370</v>
+        <v>345</v>
       </c>
       <c r="D342" s="3">
         <v>1</v>
@@ -9635,21 +9842,17 @@
       <c r="A343" s="2"/>
       <c r="B343" s="2"/>
       <c r="C343" s="5" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="D343" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A344" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="B344" s="2" t="s">
-        <v>415</v>
-      </c>
+      <c r="A344" s="2"/>
+      <c r="B344" s="2"/>
       <c r="C344" s="5" t="s">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="D344" s="3">
         <v>1</v>
@@ -9659,7 +9862,7 @@
       <c r="A345" s="2"/>
       <c r="B345" s="2"/>
       <c r="C345" s="5" t="s">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="D345" s="3">
         <v>1</v>
@@ -9669,7 +9872,7 @@
       <c r="A346" s="2"/>
       <c r="B346" s="2"/>
       <c r="C346" s="5" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="D346" s="3">
         <v>1</v>
@@ -9679,7 +9882,7 @@
       <c r="A347" s="2"/>
       <c r="B347" s="2"/>
       <c r="C347" s="5" t="s">
-        <v>351</v>
+        <v>388</v>
       </c>
       <c r="D347" s="3">
         <v>1</v>
@@ -9689,7 +9892,7 @@
       <c r="A348" s="2"/>
       <c r="B348" s="2"/>
       <c r="C348" s="5" t="s">
-        <v>352</v>
+        <v>389</v>
       </c>
       <c r="D348" s="3">
         <v>1</v>
@@ -9699,7 +9902,7 @@
       <c r="A349" s="2"/>
       <c r="B349" s="2"/>
       <c r="C349" s="5" t="s">
-        <v>353</v>
+        <v>390</v>
       </c>
       <c r="D349" s="3">
         <v>1</v>
@@ -9709,7 +9912,7 @@
       <c r="A350" s="2"/>
       <c r="B350" s="2"/>
       <c r="C350" s="5" t="s">
-        <v>354</v>
+        <v>391</v>
       </c>
       <c r="D350" s="3">
         <v>1</v>
@@ -9719,7 +9922,7 @@
       <c r="A351" s="2"/>
       <c r="B351" s="2"/>
       <c r="C351" s="5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D351" s="3">
         <v>1</v>
@@ -9729,7 +9932,7 @@
       <c r="A352" s="2"/>
       <c r="B352" s="2"/>
       <c r="C352" s="5" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D352" s="3">
         <v>1</v>
@@ -9739,7 +9942,7 @@
       <c r="A353" s="2"/>
       <c r="B353" s="2"/>
       <c r="C353" s="5" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="D353" s="3">
         <v>1</v>
@@ -9749,7 +9952,7 @@
       <c r="A354" s="2"/>
       <c r="B354" s="2"/>
       <c r="C354" s="5" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="D354" s="3">
         <v>1</v>
@@ -9759,7 +9962,7 @@
       <c r="A355" s="2"/>
       <c r="B355" s="2"/>
       <c r="C355" s="5" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="D355" s="3">
         <v>1</v>
@@ -9767,11 +9970,9 @@
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A356" s="2"/>
-      <c r="B356" s="2" t="s">
-        <v>365</v>
-      </c>
+      <c r="B356" s="2"/>
       <c r="C356" s="5" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="D356" s="3">
         <v>1</v>
@@ -9781,7 +9982,7 @@
       <c r="A357" s="2"/>
       <c r="B357" s="2"/>
       <c r="C357" s="5" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D357" s="3">
         <v>1</v>
@@ -9791,17 +9992,21 @@
       <c r="A358" s="2"/>
       <c r="B358" s="2"/>
       <c r="C358" s="5" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="D358" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A359" s="2"/>
-      <c r="B359" s="2"/>
+      <c r="A359" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B359" s="2" t="s">
+        <v>415</v>
+      </c>
       <c r="C359" s="5" t="s">
-        <v>369</v>
+        <v>348</v>
       </c>
       <c r="D359" s="3">
         <v>1</v>
@@ -9811,7 +10016,7 @@
       <c r="A360" s="2"/>
       <c r="B360" s="2"/>
       <c r="C360" s="5" t="s">
-        <v>370</v>
+        <v>349</v>
       </c>
       <c r="D360" s="3">
         <v>1</v>
@@ -9821,7 +10026,7 @@
       <c r="A361" s="2"/>
       <c r="B361" s="2"/>
       <c r="C361" s="5" t="s">
-        <v>371</v>
+        <v>350</v>
       </c>
       <c r="D361" s="3">
         <v>1</v>
@@ -9831,7 +10036,7 @@
       <c r="A362" s="2"/>
       <c r="B362" s="2"/>
       <c r="C362" s="5" t="s">
-        <v>372</v>
+        <v>351</v>
       </c>
       <c r="D362" s="3">
         <v>1</v>
@@ -9841,7 +10046,7 @@
       <c r="A363" s="2"/>
       <c r="B363" s="2"/>
       <c r="C363" s="5" t="s">
-        <v>373</v>
+        <v>352</v>
       </c>
       <c r="D363" s="3">
         <v>1</v>
@@ -9851,7 +10056,7 @@
       <c r="A364" s="2"/>
       <c r="B364" s="2"/>
       <c r="C364" s="5" t="s">
-        <v>374</v>
+        <v>353</v>
       </c>
       <c r="D364" s="3">
         <v>1</v>
@@ -9861,7 +10066,7 @@
       <c r="A365" s="2"/>
       <c r="B365" s="2"/>
       <c r="C365" s="5" t="s">
-        <v>375</v>
+        <v>354</v>
       </c>
       <c r="D365" s="3">
         <v>1</v>
@@ -9871,7 +10076,7 @@
       <c r="A366" s="2"/>
       <c r="B366" s="2"/>
       <c r="C366" s="5" t="s">
-        <v>376</v>
+        <v>355</v>
       </c>
       <c r="D366" s="3">
         <v>1</v>
@@ -9881,7 +10086,7 @@
       <c r="A367" s="2"/>
       <c r="B367" s="2"/>
       <c r="C367" s="5" t="s">
-        <v>377</v>
+        <v>358</v>
       </c>
       <c r="D367" s="3">
         <v>1</v>
@@ -9891,7 +10096,7 @@
       <c r="A368" s="2"/>
       <c r="B368" s="2"/>
       <c r="C368" s="5" t="s">
-        <v>421</v>
+        <v>444</v>
       </c>
       <c r="D368" s="3">
         <v>1</v>
@@ -9901,7 +10106,7 @@
       <c r="A369" s="2"/>
       <c r="B369" s="2"/>
       <c r="C369" s="5" t="s">
-        <v>422</v>
+        <v>359</v>
       </c>
       <c r="D369" s="3">
         <v>1</v>
@@ -9909,9 +10114,11 @@
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A370" s="2"/>
-      <c r="B370" s="2"/>
+      <c r="B370" s="2" t="s">
+        <v>365</v>
+      </c>
       <c r="C370" s="5" t="s">
-        <v>448</v>
+        <v>372</v>
       </c>
       <c r="D370" s="3">
         <v>1</v>
@@ -9921,19 +10128,17 @@
       <c r="A371" s="2"/>
       <c r="B371" s="2"/>
       <c r="C371" s="5" t="s">
-        <v>449</v>
+        <v>373</v>
       </c>
       <c r="D371" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A372" s="2" t="s">
-        <v>450</v>
-      </c>
+      <c r="A372" s="2"/>
       <c r="B372" s="2"/>
       <c r="C372" s="5" t="s">
-        <v>451</v>
+        <v>374</v>
       </c>
       <c r="D372" s="3">
         <v>1</v>
@@ -9943,7 +10148,7 @@
       <c r="A373" s="2"/>
       <c r="B373" s="2"/>
       <c r="C373" s="5" t="s">
-        <v>452</v>
+        <v>375</v>
       </c>
       <c r="D373" s="3">
         <v>1</v>
@@ -9953,19 +10158,17 @@
       <c r="A374" s="2"/>
       <c r="B374" s="2"/>
       <c r="C374" s="5" t="s">
-        <v>453</v>
+        <v>376</v>
       </c>
       <c r="D374" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A375" s="2" t="s">
-        <v>392</v>
-      </c>
+      <c r="A375" s="2"/>
       <c r="B375" s="2"/>
       <c r="C375" s="5" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="D375" s="3">
         <v>1</v>
@@ -9975,7 +10178,7 @@
       <c r="A376" s="2"/>
       <c r="B376" s="2"/>
       <c r="C376" s="5" t="s">
-        <v>394</v>
+        <v>421</v>
       </c>
       <c r="D376" s="3">
         <v>1</v>
@@ -9985,7 +10188,7 @@
       <c r="A377" s="2"/>
       <c r="B377" s="2"/>
       <c r="C377" s="5" t="s">
-        <v>395</v>
+        <v>422</v>
       </c>
       <c r="D377" s="3">
         <v>1</v>
@@ -9995,7 +10198,7 @@
       <c r="A378" s="2"/>
       <c r="B378" s="2"/>
       <c r="C378" s="5" t="s">
-        <v>396</v>
+        <v>438</v>
       </c>
       <c r="D378" s="3">
         <v>1</v>
@@ -10005,29 +10208,29 @@
       <c r="A379" s="2"/>
       <c r="B379" s="2"/>
       <c r="C379" s="5" t="s">
-        <v>397</v>
+        <v>439</v>
       </c>
       <c r="D379" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A380" s="2"/>
+      <c r="A380" s="2" t="s">
+        <v>440</v>
+      </c>
       <c r="B380" s="2"/>
       <c r="C380" s="5" t="s">
-        <v>398</v>
+        <v>441</v>
       </c>
       <c r="D380" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A381" s="2" t="s">
-        <v>129</v>
-      </c>
+      <c r="A381" s="2"/>
       <c r="B381" s="2"/>
       <c r="C381" s="5" t="s">
-        <v>130</v>
+        <v>442</v>
       </c>
       <c r="D381" s="3">
         <v>1</v>
@@ -10037,17 +10240,19 @@
       <c r="A382" s="2"/>
       <c r="B382" s="2"/>
       <c r="C382" s="5" t="s">
-        <v>131</v>
+        <v>443</v>
       </c>
       <c r="D382" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A383" s="2"/>
+      <c r="A383" s="2" t="s">
+        <v>392</v>
+      </c>
       <c r="B383" s="2"/>
       <c r="C383" s="5" t="s">
-        <v>132</v>
+        <v>393</v>
       </c>
       <c r="D383" s="3">
         <v>1</v>
@@ -10057,7 +10262,7 @@
       <c r="A384" s="2"/>
       <c r="B384" s="2"/>
       <c r="C384" s="5" t="s">
-        <v>133</v>
+        <v>394</v>
       </c>
       <c r="D384" s="3">
         <v>1</v>
@@ -10066,50 +10271,84 @@
     <row r="385" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A385" s="2"/>
       <c r="B385" s="2"/>
-      <c r="C385" s="7"/>
-      <c r="D385" s="3"/>
+      <c r="C385" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="D385" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A386" s="2"/>
       <c r="B386" s="2"/>
-      <c r="C386" s="7"/>
-      <c r="D386" s="3"/>
+      <c r="C386" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="D386" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A387" s="2"/>
       <c r="B387" s="2"/>
-      <c r="C387" s="7"/>
-      <c r="D387" s="3"/>
+      <c r="C387" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="D387" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A388" s="2"/>
       <c r="B388" s="2"/>
-      <c r="C388" s="7"/>
-      <c r="D388" s="3"/>
+      <c r="C388" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="D388" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A389" s="2"/>
+      <c r="A389" s="2" t="s">
+        <v>129</v>
+      </c>
       <c r="B389" s="2"/>
-      <c r="C389" s="7"/>
-      <c r="D389" s="3"/>
+      <c r="C389" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D389" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A390" s="2"/>
       <c r="B390" s="2"/>
-      <c r="C390" s="7"/>
-      <c r="D390" s="3"/>
+      <c r="C390" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D390" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A391" s="2"/>
       <c r="B391" s="2"/>
-      <c r="C391" s="7"/>
-      <c r="D391" s="3"/>
+      <c r="C391" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D391" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A392" s="2"/>
       <c r="B392" s="2"/>
-      <c r="C392" s="7"/>
-      <c r="D392" s="3"/>
+      <c r="C392" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D392" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A393" s="2"/>
@@ -10203,7 +10442,7 @@
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A408" s="2"/>
-      <c r="B408" s="5"/>
+      <c r="B408" s="2"/>
       <c r="C408" s="7"/>
       <c r="D408" s="3"/>
     </row>
@@ -10222,111 +10461,127 @@
     <row r="411" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A411" s="2"/>
       <c r="B411" s="2"/>
-      <c r="C411" s="5"/>
+      <c r="C411" s="7"/>
       <c r="D411" s="3"/>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A412" s="2"/>
       <c r="B412" s="2"/>
-      <c r="C412" s="5"/>
+      <c r="C412" s="7"/>
       <c r="D412" s="3"/>
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A413" s="2"/>
       <c r="B413" s="2"/>
-      <c r="C413" s="5"/>
+      <c r="C413" s="7"/>
       <c r="D413" s="3"/>
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A414" s="2"/>
       <c r="B414" s="2"/>
-      <c r="C414" s="5"/>
+      <c r="C414" s="7"/>
       <c r="D414" s="3"/>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A415" s="2"/>
       <c r="B415" s="2"/>
-      <c r="C415" s="2"/>
+      <c r="C415" s="7"/>
       <c r="D415" s="3"/>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A416" s="2"/>
-      <c r="B416" s="2"/>
-      <c r="C416" s="2"/>
+      <c r="B416" s="5"/>
+      <c r="C416" s="7"/>
       <c r="D416" s="3"/>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A417" s="2"/>
       <c r="B417" s="2"/>
-      <c r="C417" s="2"/>
+      <c r="C417" s="7"/>
       <c r="D417" s="3"/>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A418" s="2"/>
       <c r="B418" s="2"/>
-      <c r="C418" s="2"/>
+      <c r="C418" s="7"/>
       <c r="D418" s="3"/>
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A419" s="2"/>
       <c r="B419" s="2"/>
-      <c r="C419" s="2"/>
+      <c r="C419" s="5"/>
       <c r="D419" s="3"/>
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A420" s="2"/>
       <c r="B420" s="2"/>
-      <c r="C420" s="2"/>
+      <c r="C420" s="5"/>
       <c r="D420" s="3"/>
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A421" s="2"/>
       <c r="B421" s="2"/>
-      <c r="C421" s="2"/>
+      <c r="C421" s="5"/>
       <c r="D421" s="3"/>
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A422" s="2"/>
       <c r="B422" s="2"/>
-      <c r="C422" s="2"/>
+      <c r="C422" s="5"/>
       <c r="D422" s="3"/>
     </row>
-    <row r="433" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="434" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="435" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="436" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="437" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="438" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="439" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="440" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="441" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="442" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="443" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="444" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="445" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="446" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="447" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="448" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="449" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="450" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="451" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="452" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="453" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="454" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="455" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="456" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="457" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="458" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="459" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="460" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="461" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="462" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="463" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="464" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A423" s="2"/>
+      <c r="B423" s="2"/>
+      <c r="C423" s="2"/>
+      <c r="D423" s="3"/>
+    </row>
+    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A424" s="2"/>
+      <c r="B424" s="2"/>
+      <c r="C424" s="2"/>
+      <c r="D424" s="3"/>
+    </row>
+    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A425" s="2"/>
+      <c r="B425" s="2"/>
+      <c r="C425" s="2"/>
+      <c r="D425" s="3"/>
+    </row>
+    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A426" s="2"/>
+      <c r="B426" s="2"/>
+      <c r="C426" s="2"/>
+      <c r="D426" s="3"/>
+    </row>
+    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A427" s="2"/>
+      <c r="B427" s="2"/>
+      <c r="C427" s="2"/>
+      <c r="D427" s="3"/>
+    </row>
+    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A428" s="2"/>
+      <c r="B428" s="2"/>
+      <c r="C428" s="2"/>
+      <c r="D428" s="3"/>
+    </row>
+    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A429" s="2"/>
+      <c r="B429" s="2"/>
+      <c r="C429" s="2"/>
+      <c r="D429" s="3"/>
+    </row>
+    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A430" s="2"/>
+      <c r="B430" s="2"/>
+      <c r="C430" s="2"/>
+      <c r="D430" s="3"/>
+    </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="C11:C12" name="Tags_1_3_1"/>
-    <protectedRange sqref="C16" name="Tags_1_3_1_3"/>
+    <protectedRange sqref="C15:C16" name="Tags_1_3_1"/>
+    <protectedRange sqref="C20" name="Tags_1_3_1_3"/>
   </protectedRanges>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
